--- a/output/full_scan/batch_seq3_2026-10-22.xlsx
+++ b/output/full_scan/batch_seq3_2026-10-22.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O222"/>
+  <dimension ref="A1:O223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>59.80106338323931</v>
+        <v>59.80106338864974</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>14.23539164168953</v>
+        <v>14.23539171888559</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>5.604635508237373</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.394477013814408</v>
+        <v>0.3944770132433513</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>59.5743107903958</v>
+        <v>59.57431076949047</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>21.01834377340828</v>
+        <v>21.01834392022064</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.5050085910566</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.05734851960389631</v>
+        <v>-0.05734852012305858</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>70.3875801384481</v>
+        <v>70.38758018822661</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>32.04339978158151</v>
+        <v>32.04339983812174</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>1.678069002562811</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>60.56630407841722</v>
+        <v>60.56630408944484</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>25.10586992887248</v>
+        <v>25.10586990843579</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1.195403088141908</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.01952106084073724</v>
+        <v>-0.01952106077584859</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>55.67333605851064</v>
+        <v>55.67333607508785</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>29.57014563863146</v>
+        <v>29.57014577946339</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0.8223457768484115</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1599015876396956</v>
+        <v>-0.1599015880031063</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>66.87720070462821</v>
+        <v>66.8772007103008</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>37.41848757762833</v>
+        <v>37.41848755986882</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1.346346242874108</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1701029439444335</v>
+        <v>0.1701029440742234</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>69.72865349618573</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>36.34536839792073</v>
+        <v>36.34536836779114</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>0.7157272660294796</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.8665002602747509</v>
+        <v>0.8665002604045191</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>59.95831237993474</v>
+        <v>59.95831240995898</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>26.91253659744132</v>
+        <v>26.91253666583384</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>0.7455094456534527</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.0292070479862577</v>
+        <v>0.02920704796029795</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>72.97433622701053</v>
+        <v>72.97433627816002</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>42.98956749653622</v>
+        <v>42.98956776231916</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>2.945998223547903</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.6009604054668403</v>
+        <v>0.600960404791957</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>61.55664833420636</v>
+        <v>61.55664834391103</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>28.25304264657005</v>
+        <v>28.2530427122574</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>0.6907989432775367</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.9562086143774282</v>
+        <v>0.9562086139880579</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>76.22529625164339</v>
+        <v>76.22529626477993</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>42.13003390490586</v>
+        <v>42.13003386972692</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>1.12505222899752</v>
@@ -1121,7 +1121,7 @@
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>915.4542895795605</v>
+        <v>915.4542895795606</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>29.9</v>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>69.83717360850238</v>
+        <v>69.8371736026926</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>44.73862634218306</v>
+        <v>44.73862637463653</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1.015748146531154</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.07537932146955773</v>
+        <v>0.07537932150849258</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>905.0940204420203</v>
+        <v>905.0940204420202</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>261</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>77.97248145819822</v>
+        <v>77.97248146523248</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>63.95874262972839</v>
+        <v>63.95874263706654</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>2.342619311936744</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>6.235141421712743</v>
+        <v>6.235141421401252</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>57.95758490094727</v>
+        <v>57.95758493928318</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>30.19177213704293</v>
+        <v>30.19177216770548</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>1.852443641606935</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.4142874188313246</v>
+        <v>0.4142874182602796</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>887.7144549724198</v>
+        <v>887.71445497242</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>74.90000000000001</v>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>67.19417187947718</v>
+        <v>67.19417189418813</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>25.02700820768923</v>
+        <v>25.02700816648467</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>1.012030917740277</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.4693127943789088</v>
+        <v>0.4693127944437998</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>71.36493482701881</v>
+        <v>71.36493483598061</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>43.79753154999033</v>
+        <v>43.79753157404687</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1.075990154397204</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.166282915825408</v>
+        <v>0.1662829158773194</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>72.57483594189316</v>
+        <v>72.57483591813846</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>34.70793804270247</v>
+        <v>34.70793810919041</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>1.012925788046394</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.4739233418365224</v>
+        <v>0.4739233420312057</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>71.81952205135931</v>
+        <v>71.81952205893865</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>40.86436919443523</v>
+        <v>40.8643692108154</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>1.042553710793667</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.1196680481505785</v>
+        <v>0.1196680481895162</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>67.41933170868896</v>
+        <v>67.41933173821209</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>51.72762976718296</v>
+        <v>51.72762983052566</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>0.5617301792409402</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.9178057502046899</v>
+        <v>0.9178057492961589</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>61.60081271830911</v>
+        <v>61.6008127995416</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>25.11068052408052</v>
+        <v>25.11068070356847</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.7364609538964125</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>4.391973181397504</v>
+        <v>4.391973179580498</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>816.5579697323936</v>
+        <v>816.5579697323935</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>15.55</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>61.09070856766704</v>
+        <v>61.09070851136455</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>43.50401938071098</v>
+        <v>43.50401940642036</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>4.375687555940727</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.008889902640746933</v>
+        <v>-0.008889902627768287</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>813.5424470797767</v>
+        <v>813.5424470797773</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>32.2</v>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>62.60627130695084</v>
+        <v>62.60627147029199</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>18.50681539283264</v>
+        <v>18.50681536615268</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>1.277648133410794</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.09613519008586949</v>
+        <v>0.09613518994310263</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>57.60691599676174</v>
+        <v>57.60691593959687</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>36.54044687983089</v>
+        <v>36.5404469071664</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>0.7889967476135447</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.252847675711692</v>
+        <v>-0.2528476756338192</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>56.2722725072543</v>
+        <v>56.27227254296977</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>15.77993508584586</v>
+        <v>15.77993526242127</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>0.9023181740181346</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.4781863714179724</v>
+        <v>-0.4781863716775545</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>770.361911263209</v>
+        <v>770.3619112632089</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>100.5</v>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>53.21492226709724</v>
+        <v>53.2149222848541</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>28.9635895332753</v>
+        <v>28.96358975411489</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>0.6877168930930208</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.2257499365230164</v>
+        <v>-0.225749936782583</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>64.55989984121504</v>
+        <v>64.55989995637165</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>44.87447147226888</v>
+        <v>44.8744714858167</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>1.604622719870239</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.3136849678717313</v>
+        <v>0.3136849674823636</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>64.9184245578179</v>
+        <v>64.91842471822744</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>21.27725275403824</v>
+        <v>21.277252736604</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>1.337822769850339</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.078717188156809</v>
+        <v>0.07871718814383158</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>59.68174458176957</v>
+        <v>59.68173919797805</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>39.04824858632512</v>
+        <v>39.04824946982505</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>3.448151378147454</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.03402947463530415</v>
+        <v>-0.03402947072829066</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>56.34456245247537</v>
+        <v>56.34456258921541</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>34.33020248644928</v>
+        <v>34.33020246666523</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.4659466481919292</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.01346586618491269</v>
+        <v>-0.01346586626278645</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>717.4339295706779</v>
+        <v>717.4339295706784</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>22.35</v>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>52.06591075574185</v>
+        <v>52.0659108694322</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>32.80356093612767</v>
+        <v>32.80356099549325</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>0.6582301498904217</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.0190634808274156</v>
+        <v>-0.01906348111294354</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>67.90867564496037</v>
+        <v>67.90867568939041</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>36.74719987525796</v>
+        <v>36.74719989276585</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.7588037569183914</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.09395232943775722</v>
+        <v>0.09395232939881959</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>65.3727122022143</v>
+        <v>65.37271236483534</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>32.4664017228581</v>
+        <v>32.46640172285811</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0.7860595746945929</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>1.581722323027372</v>
+        <v>1.581722322248676</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>705.3764098888114</v>
+        <v>705.3764098888115</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>113.5</v>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>54.01002527835742</v>
+        <v>54.01002527128808</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>27.02462033625183</v>
+        <v>27.02462030355594</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.8675822415334251</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.2071288467064245</v>
+        <v>-0.2071288464208894</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>40.85927612607981</v>
+        <v>40.85927606532302</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>22.28756628493909</v>
+        <v>22.2875662849391</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.7501028772475842</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.337223915758043</v>
+        <v>0.33722391587486</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>50.46315435923908</v>
+        <v>50.46315436957536</v>
       </c>
       <c r="I36" s="2" t="n">
         <v>24.37396637774441</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.2557313967079072</v>
+        <v>-0.2557313966819436</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>673.1863457397021</v>
+        <v>673.1863457397013</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>158.5</v>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>58.56479686093574</v>
+        <v>58.56479690306092</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>29.74885911373298</v>
+        <v>29.74885907595943</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>0.6465001609567638</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.3772688426696105</v>
+        <v>-0.3772688425138533</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>658.1266246236502</v>
+        <v>658.1266246236509</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>18.25</v>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>54.40012780986535</v>
+        <v>54.40012780037176</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>8.061458025720054</v>
+        <v>8.061457714129059</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>9.747582263852564</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.1477715004654256</v>
+        <v>0.147771500556278</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>49.1157418073961</v>
+        <v>49.11574183775809</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>32.53853441562241</v>
+        <v>32.53853449291717</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.3166670520886173</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.8632749645815307</v>
+        <v>-0.8632749651006923</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>58.61145733807253</v>
+        <v>58.61145736496871</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>38.84382279764777</v>
+        <v>38.84382277092594</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.4595582803252993</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.03912638855893524</v>
+        <v>0.03912638850702632</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>53.78377294704126</v>
+        <v>53.78377298671629</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>19.764868216628</v>
+        <v>19.76486825815594</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.370066424675075</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.00193357941754322</v>
+        <v>-0.001933579425331282</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>637.2661791471982</v>
+        <v>637.266179147198</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>368</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.27980685718725</v>
+        <v>51.27980686321779</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>27.80058402393605</v>
+        <v>27.80058416202355</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>1.6584113968261</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-3.240398616585765</v>
+        <v>-3.240398617182777</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>41.50469370452103</v>
+        <v>41.50469369934297</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>37.79536708770893</v>
+        <v>37.79536723289028</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.2859672388961456</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-2.316049272318159</v>
+        <v>-2.31604927243496</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>57.29012268313159</v>
+        <v>57.29012261833646</v>
       </c>
       <c r="I44" s="2" t="n">
         <v>47.71210525077854</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>51.79704113944786</v>
+        <v>51.79704035366276</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>13.57134023593671</v>
+        <v>13.57134028446269</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.900219540004771</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.03376423164302006</v>
+        <v>0.03376423166897904</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>592.9991933331629</v>
+        <v>592.999193333157</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>14.55</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>52.27073687654863</v>
+        <v>52.27073651931214</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>21.58634612515898</v>
+        <v>21.58634612234723</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.9724630380057481</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.002208630605850248</v>
+        <v>0.002208630527979677</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>590.9638550309359</v>
+        <v>590.9638550309338</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>170</v>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>59.11154140561391</v>
+        <v>59.11154153666048</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>11.94416909905418</v>
+        <v>11.94416911514913</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>1.244584445629161</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.5847032194116653</v>
+        <v>0.5847032188925095</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>53.23795182289529</v>
+        <v>53.23795175434103</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>23.1046868859595</v>
+        <v>23.10468692030992</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.4448238616571399</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.01978194886063678</v>
+        <v>-0.01978194795213106</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>55.0595285960035</v>
+        <v>55.05952863057924</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>51.88711351913491</v>
+        <v>51.88711367675793</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.6445124292071772</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.006513496985684153</v>
+        <v>-0.00651349703760129</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>574.5518085642991</v>
+        <v>574.551808564299</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>20.5</v>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>51.14743328398848</v>
+        <v>51.1474334275975</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>17.17305451906723</v>
+        <v>17.17305453666027</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.7993140433268333</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.02130324994222731</v>
+        <v>0.02130324992924805</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>45.83365821130152</v>
+        <v>45.83365822200719</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>18.95029046389751</v>
+        <v>18.9502907906515</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>1.343156454907459</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-24.44575063370426</v>
+        <v>-24.4457506363</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>57.50850865524534</v>
+        <v>57.50850895102734</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>44.25731243368071</v>
+        <v>44.25731262521241</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.87146289226673</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.02672480602731375</v>
+        <v>0.02672480584560599</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>53.63898611347946</v>
+        <v>53.63898612800837</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>29.2156259519511</v>
+        <v>29.21562606844949</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.4380875863965594</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.07402694751652716</v>
+        <v>-0.07402694764631579</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>46.83110001653554</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>27.22811857833856</v>
+        <v>27.228118743154</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.2724889263666855</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.3751208464864444</v>
+        <v>-0.3751208465902734</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>54.59254701625644</v>
+        <v>54.59254701224169</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>37.19820831881184</v>
+        <v>37.19820826043623</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>0.469779550763363</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0513033432897454</v>
+        <v>0.05130334330272124</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>46.33936668651702</v>
+        <v>46.33936668913353</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>35.99538127961777</v>
+        <v>35.99538136743533</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>0.3107656274756301</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-5.440734089155244</v>
+        <v>-5.440734089246096</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>52.21280654280857</v>
+        <v>52.21280626217998</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>13.82071578173521</v>
+        <v>13.8207160346565</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>1.975161497612949</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.02133352098558193</v>
+        <v>-0.02133352082983971</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>54.95694218247269</v>
+        <v>54.95694222161737</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>24.64764202617361</v>
+        <v>24.64764204161234</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.6003634011673895</v>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>46.79175363574848</v>
+        <v>46.79175362430315</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>13.29896711064278</v>
+        <v>13.29896717062897</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>1.665316563296289</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.2165691498742448</v>
+        <v>-0.216569149915438</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>48.92002955703256</v>
+        <v>48.92002952796356</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>6.171766243587715</v>
+        <v>6.171766270509021</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>1.556703646938216</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.09385382327694047</v>
+        <v>-0.09385382317310836</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>53.07665971654347</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>42.70906448659041</v>
+        <v>42.70906458386892</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.7610589791480448</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.2267510110204413</v>
+        <v>-0.2267510110463978</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>52.3797993605915</v>
+        <v>52.37979936993211</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>17.89227280697869</v>
+        <v>17.89227277898258</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>0.9409445925915478</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.1645175485732686</v>
+        <v>-0.1645175485343277</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>41.05162872673978</v>
+        <v>41.05162903541824</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>7.093919715924004</v>
+        <v>7.093919683293741</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.9936198555364365</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.03214089797578867</v>
+        <v>0.03214089849494517</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>47.48104037146116</v>
+        <v>47.48104039272584</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>32.89498630156256</v>
+        <v>32.89498636856455</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.4301642365648293</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.744023004918265</v>
+        <v>-0.744023004970185</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>53.56875357961145</v>
+        <v>53.56875359848696</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>35.67246138824486</v>
+        <v>35.67246141932844</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.9352769891595933</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.17143965157651</v>
+        <v>-0.1714396517412755</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>53.89454121312844</v>
+        <v>53.89454114211946</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>35.01620627433259</v>
+        <v>35.01620626703629</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.4909582591832417</v>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>46.83028280562051</v>
+        <v>46.83028306484713</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>22.65372898798383</v>
+        <v>22.65372910514331</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>1.105926777129552</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.02064688752578368</v>
+        <v>0.02064688747386842</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>500.6513091358428</v>
+        <v>500.6513091358423</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>144</v>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>51.36212100854866</v>
+        <v>51.36212090435313</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10.34999968805236</v>
+        <v>10.34999990475773</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>0.9329043384208081</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0207151946550087</v>
+        <v>-0.02071519400603854</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>53.08371503829029</v>
+        <v>53.08371503291552</v>
       </c>
       <c r="I69" s="2" t="n">
         <v>37.12994939153366</v>
@@ -4142,7 +4142,7 @@
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>499.3231216156407</v>
+        <v>499.3231216156408</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>57.8</v>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>47.65306052375151</v>
+        <v>47.65306062265842</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>10.31993072878301</v>
+        <v>10.31993087098116</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.8048861985460785</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.153564372052891</v>
+        <v>-0.1535643723124661</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>497.4575897825753</v>
+        <v>497.4575897825754</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>32.65</v>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>49.07252878773991</v>
+        <v>49.07252872741659</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>4.699080669930233</v>
+        <v>4.699080741282998</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>2.520646498963303</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>51.91340412453101</v>
+        <v>51.9134041682323</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>29.16926004728491</v>
+        <v>29.16926024517759</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>1.206872808767379</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-3.542475729005439</v>
+        <v>-3.542475732899128</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>44.54392531263706</v>
+        <v>44.54392530633835</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>19.79512365174058</v>
+        <v>19.79512375067669</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.5253873156560308</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.207755659779393</v>
+        <v>-0.2077556598313061</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>43.17182352724873</v>
+        <v>43.17182357422524</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>12.69403452814511</v>
+        <v>12.69403486399327</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.800702741839606</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-41.23375757466556</v>
+        <v>-41.23375759257596</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>485.16088126199</v>
+        <v>485.1608812619963</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>18</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>43.87524358356951</v>
+        <v>43.87524360766981</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>31.13029364511235</v>
+        <v>31.13029377551366</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.5614772909929824</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.1624460693237277</v>
+        <v>-0.1624460694535121</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>42.77477783035452</v>
+        <v>42.77477790833077</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>22.97709408778836</v>
+        <v>22.97709434011112</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.6367793481253671</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.5336835378104765</v>
+        <v>-0.5336835380700472</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>46.68948863705769</v>
+        <v>46.6894886384186</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>25.99309169285941</v>
+        <v>25.99309183061177</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>1.040022166993571</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-10.94021187415198</v>
+        <v>-10.94021187448947</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>478.4223458335379</v>
+        <v>478.4223458335378</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>121.5</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>51.78696168334828</v>
+        <v>51.78696267233168</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>22.8663560903599</v>
+        <v>22.86635621813099</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.6072533339872901</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.3421922643651798</v>
+        <v>0.3421922629375248</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>46.84103542782626</v>
+        <v>46.8410354703251</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>11.95972618126904</v>
+        <v>11.95972621701783</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>0.8859614575116446</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.1032389035323085</v>
+        <v>-0.1032389038437878</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>470.493407450892</v>
+        <v>470.4934074508921</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>92.40000000000001</v>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>48.70681825961081</v>
+        <v>48.70681820029864</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>8.683878268055693</v>
+        <v>8.683878231249357</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>0.4978967031178403</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.2182118606289978</v>
+        <v>0.2182118607587886</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>469.4531154279457</v>
+        <v>469.4531154279458</v>
       </c>
       <c r="E81" s="2" t="n">
         <v>486</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>45.27691188227703</v>
+        <v>45.27691188389444</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>24.4282015139967</v>
+        <v>24.42820179900988</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>1.013953057957626</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-13.44172837707058</v>
+        <v>-13.44172837753777</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>53.81149372930365</v>
+        <v>53.81149372592903</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>21.26580535265016</v>
+        <v>21.26580545517053</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>2.44493620307061</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.07221827427501304</v>
+        <v>-0.07221827432693295</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>452.4168311817842</v>
+        <v>452.4168311817843</v>
       </c>
       <c r="E83" s="2" t="n">
         <v>467</v>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>39.27163588804801</v>
+        <v>39.27163587314165</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>25.8437221889719</v>
+        <v>25.8437223703811</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.6573905201305341</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-12.86534648600197</v>
+        <v>-12.86534648587221</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>45.20809504289365</v>
+        <v>45.20809505364588</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>28.00637377394791</v>
+        <v>28.00637378519643</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.495486720427454</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-1.10147953400501</v>
+        <v>-1.101479534108838</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>448.822778712089</v>
+        <v>448.8227787120892</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>18.55</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>48.1274156157905</v>
+        <v>48.12741572943356</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>23.87526019395285</v>
+        <v>23.87526020994164</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.4752929231042735</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.03730053274174996</v>
+        <v>-0.03730053305323908</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>38.9419256725057</v>
+        <v>38.94192766538842</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>22.50332029402502</v>
+        <v>22.50332397506807</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.5278350593087376</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.518895244320812</v>
+        <v>-0.5188952505505799</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>445.6230679708156</v>
+        <v>445.623067970821</v>
       </c>
       <c r="E87" s="2" t="n">
         <v>38.3</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>48.37121691375533</v>
+        <v>48.37121670485817</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>13.53951254477261</v>
+        <v>13.53951277386313</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>0.8245432064596556</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.04616740224395854</v>
+        <v>0.04616740250353066</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>51.38553186660084</v>
+        <v>51.38553168735976</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12.52878679245343</v>
+        <v>12.52878689794829</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>1.712522405083917</v>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>47.47114516062299</v>
+        <v>47.47114522904082</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>20.2017569671261</v>
+        <v>20.20175714427729</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.8767545255598808</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.3229094774618758</v>
+        <v>-0.322909477773369</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>41.17553343793086</v>
+        <v>41.17553352191479</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>26.51123805135544</v>
+        <v>26.51123823387077</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>0.7034666490389513</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.5489737198559039</v>
+        <v>-0.5489737205048462</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>42.64083883038509</v>
+        <v>42.64083891130211</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>22.24614761473033</v>
+        <v>22.24614772171642</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>0.730259044475385</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-2.787742601178786</v>
+        <v>-2.787742601438355</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>43.73970541015106</v>
+        <v>43.73970544791885</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>27.35387340462318</v>
+        <v>27.35387349526748</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.5688715334330581</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.3638841273651791</v>
+        <v>-0.3638841275339031</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>49.40485575304002</v>
+        <v>49.40485580410974</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>28.44968741703683</v>
+        <v>28.44968757341286</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.8371232499983399</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.5023187367079327</v>
+        <v>-0.5023187368247415</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>52.08657055221313</v>
+        <v>52.08657065436058</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>18.59101763262185</v>
+        <v>18.59101773768113</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.9528190605725229</v>
@@ -5467,7 +5467,7 @@
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>436.4266321632578</v>
+        <v>436.4266321632602</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>114</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>32.36137709474903</v>
+        <v>32.36137707409225</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>16.00203833675969</v>
+        <v>16.00203831060637</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>1.873961677944835</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>45.67077946533448</v>
+        <v>45.67077965126089</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>23.03758088776937</v>
+        <v>23.03758103609027</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.5488713602307305</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.02611821191400162</v>
+        <v>-0.0261182120827266</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>44.42015877931095</v>
+        <v>44.42015875163243</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>18.26833913340374</v>
+        <v>18.26833914559043</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>0.6509163934228407</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1473318737893053</v>
+        <v>-0.1473318738282373</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>41.9104312674482</v>
+        <v>41.91043120488222</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>21.77370879894732</v>
+        <v>21.77370867469745</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>1.071238337311583</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-5.052638558246398</v>
+        <v>-5.052638557597456</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>40.41598115469303</v>
+        <v>40.41598142204839</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>14.32298936492972</v>
+        <v>14.3229895718893</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.6470130511401305</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1859809137532273</v>
+        <v>-0.1859809144800392</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>42.07377413739027</v>
+        <v>42.07377420652987</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>26.14643309346482</v>
+        <v>26.14643316198458</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>1.060399340896713</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.03868517851126553</v>
+        <v>-0.03868517845935211</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>49.95121100298546</v>
+        <v>49.95121067066705</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>15.4295246199147</v>
+        <v>15.42952483037219</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.8483701382935951</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.09717705928038067</v>
+        <v>-0.09717705785272091</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>45.81511406172431</v>
+        <v>45.81511446468344</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>17.8070980142416</v>
+        <v>17.80709823300852</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>1.749871058291456</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.1896641005385761</v>
+        <v>-0.1896641008760265</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5905,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>34.88685915742664</v>
+        <v>34.88685929106849</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>20.66932932847887</v>
+        <v>20.66932945865431</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.8177079606498702</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-3.870409539355125</v>
+        <v>-3.870409543508266</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>49.10953949792686</v>
+        <v>49.10953948404911</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>27.07647871348174</v>
+        <v>27.07647882051887</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.6988683902914974</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.02529868876308378</v>
+        <v>-0.02529868885393266</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>33.8577318976477</v>
+        <v>33.85773190159377</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>22.67298569207369</v>
+        <v>22.67298570290092</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.8222255124153995</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-107.8966566984271</v>
+        <v>-107.8966567010225</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>390.4970989782857</v>
+        <v>390.497098978286</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>298</v>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>36.98827071174825</v>
+        <v>36.98827083033219</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>14.52571182522546</v>
+        <v>14.52571195555533</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>1.307479480645701</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-1.97428306703683</v>
+        <v>-1.974283070021924</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>390.1092336294538</v>
+        <v>390.1092336294535</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>91.5</v>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>49.77105746352034</v>
+        <v>49.77105735130201</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>27.41673741674384</v>
+        <v>27.41673746286032</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.7679384861856485</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.1257648220925294</v>
+        <v>-0.1257648218329566</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>46.75640551882233</v>
+        <v>46.75640556158162</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>18.89521178662483</v>
+        <v>18.89521193480687</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.607927533512832</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-2.321480759984244</v>
+        <v>-2.321480761152322</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>2618</v>
+        <v>3055</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>蔚華科</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>377.8075356571304</v>
+        <v>378.8388084430744</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>42.2</v>
+        <v>143</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,49 +6223,49 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>48.65669564662615</v>
+        <v>37.81689925853425</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>15.14932072999743</v>
+        <v>37.11102370471477</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.7185551512186255</v>
+        <v>0.1518974943607057</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M109" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.02234942008779334</v>
+        <v>-8.876823159094666</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>2515</v>
+        <v>2618</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>中工</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>377.3845010997541</v>
+        <v>377.8075356571305</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>11.7</v>
+        <v>42.2</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>41.87114726558742</v>
+        <v>48.65669568902257</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>20.55425331747881</v>
+        <v>15.14932077220113</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.319899338045222</v>
+        <v>0.7185551512186255</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.01435131428179981</v>
+        <v>-0.02234942004885457</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>2453</v>
+        <v>2515</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>凌群</t>
+          <t>中工</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>376.0715795091467</v>
+        <v>377.3845010997571</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>53.1</v>
+        <v>11.7</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>50.59434833343481</v>
+        <v>41.87114738784366</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>18.02081362527329</v>
+        <v>20.55425339470697</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.691879909301246</v>
+        <v>1.319899338045222</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.06075486932211477</v>
+        <v>-0.01435131430775665</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>volume_break, avoid_chase, foreign_buy_3d, stronger_than_market</t>
+          <t>avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>3033</v>
+        <v>2453</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>威健</t>
+          <t>凌群</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>362.9298083901622</v>
+        <v>376.0715795091467</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>41.6</v>
+        <v>53.1</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>42.66209909192771</v>
+        <v>50.59434824800838</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>14.0939130611557</v>
+        <v>18.02081375887622</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5308942743097778</v>
+        <v>1.691879909301246</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.06231741458076329</v>
+        <v>-0.06075486939998297</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>2511</v>
+        <v>3033</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>太子</t>
+          <t>威健</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>362.2969610503523</v>
+        <v>362.9298083901622</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>8.09</v>
+        <v>41.6</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>27.37457651775827</v>
+        <v>42.6620991251279</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>20.45299489901795</v>
+        <v>14.09391322444818</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.9839021880430603</v>
+        <v>0.5308942743097778</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.01649831255771116</v>
+        <v>0.06231741448990902</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>3006</v>
+        <v>2511</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>晶豪科</t>
+          <t>太子</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>360.4017068205664</v>
+        <v>362.296961050352</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>234</v>
+        <v>8.09</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,49 +6488,49 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>39.53712844703568</v>
+        <v>27.37457659809145</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>19.76388178707239</v>
+        <v>20.45299496271462</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.6324881264386338</v>
+        <v>0.9839021880430603</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-3.536874083687048</v>
+        <v>-0.01649831257588159</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, stronger_than_market</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>2702</v>
+        <v>3006</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>華園</t>
+          <t>晶豪科</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>359.549763818719</v>
+        <v>360.4017068205664</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>11.95</v>
+        <v>234</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,49 +6541,49 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>35.616374714432</v>
+        <v>39.53712844647093</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>26.79518251213511</v>
+        <v>19.76388185797643</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.9786826390194551</v>
+        <v>0.6324881264386338</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.01476299438153969</v>
+        <v>-3.536874083687048</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>2910</v>
+        <v>2702</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>統領</t>
+          <t>華園</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>357.6038764949407</v>
+        <v>359.5497638187189</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>23.2</v>
+        <v>11.95</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>51.18469251255304</v>
+        <v>35.61637468899596</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>13.04899237994306</v>
+        <v>26.79518263809319</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.946101691395583</v>
+        <v>0.9786826390194551</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.09375032796634275</v>
+        <v>-0.01476299439451786</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, avoid_chase, hist_turn_positive, stronger_than_market</t>
+          <t>avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>2485</v>
+        <v>2910</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>兆赫</t>
+          <t>統領</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>357.3822501515434</v>
+        <v>357.6038764949407</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>38.4</v>
+        <v>23.2</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>43.6227883786962</v>
+        <v>51.18469204515686</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>23.88707692753053</v>
+        <v>13.04898601508897</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.5576500610456288</v>
+        <v>0.946101691395583</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.2542850800167507</v>
+        <v>0.09375033336547733</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, avoid_chase, hist_turn_positive, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>2451</v>
+        <v>2485</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>兆赫</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>357.3466469860892</v>
+        <v>357.3822501515434</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>275</v>
+        <v>38.4</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,49 +6700,49 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>45.53355182796523</v>
+        <v>43.62278840272374</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>14.75517577408423</v>
+        <v>23.88707707555657</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.7428449495528359</v>
+        <v>0.5576500610456288</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.986690373983798</v>
+        <v>-0.2542850801335612</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, stronger_than_market</t>
+          <t>avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>3092</v>
+        <v>2451</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>鴻碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>357.1473481669736</v>
+        <v>357.3466469860892</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>23.2</v>
+        <v>275</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,49 +6753,49 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>46.86021110136355</v>
+        <v>45.53355186422015</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>17.69051562008613</v>
+        <v>14.75517586352564</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.4152552316399888</v>
+        <v>0.7428449495528359</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L119" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.004736167643421052</v>
+        <v>-0.9866903745029569</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>2547</v>
+        <v>3092</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>日勝生</t>
+          <t>鴻碩</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>355.2117365649197</v>
+        <v>357.1473481669603</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>23.2</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>49.19516816869429</v>
+        <v>46.86021114489331</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>13.14299959796697</v>
+        <v>17.69051572864241</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.7818919386444556</v>
+        <v>0.4152552316399888</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.02162618092646629</v>
+        <v>-0.004736167786185443</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, foreign_buy_3d, stronger_than_market</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>2524</v>
+        <v>2547</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>京城</t>
+          <t>日勝生</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>354.5976336285177</v>
+        <v>355.2117365649196</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>33.2</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>41.94658401479762</v>
+        <v>49.19516831585831</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>8.270901374984806</v>
+        <v>13.14299964974114</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.5106968315253584</v>
+        <v>0.7818919386444556</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.03748475150729835</v>
+        <v>0.02162618087455014</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>2646</v>
+        <v>2524</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>星宇航空</t>
+          <t>京城</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>354.4802821017176</v>
+        <v>354.5976336285177</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>20.15</v>
+        <v>33.2</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,49 +6912,49 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>46.54946316906371</v>
+        <v>41.9465845092606</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>17.0637953600231</v>
+        <v>8.270901397840115</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.8636088952282992</v>
+        <v>0.5106968315253584</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.02097689944856439</v>
+        <v>-0.03748475168900461</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>2478</v>
+        <v>2646</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>大毅</t>
+          <t>星宇航空</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>352.384746231875</v>
+        <v>354.4802821017176</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>118.5</v>
+        <v>20.15</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,49 +6965,49 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>43.94160227671752</v>
+        <v>46.54946329495967</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>14.04352402346748</v>
+        <v>17.06379536879247</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.8847943368095003</v>
+        <v>0.8636088952282992</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M123" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.9966979248390768</v>
+        <v>0.02097689940962885</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>3008</v>
+        <v>2478</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>大毅</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>351.7129569569794</v>
+        <v>352.384746231875</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>6175</v>
+        <v>118.5</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,49 +7018,49 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>45.96235809548261</v>
+        <v>43.94160228087711</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>13.78237985643971</v>
+        <v>14.04352420528384</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.6587573071978704</v>
+        <v>0.8847943368095003</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L124" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-99.3780242384273</v>
+        <v>-0.9966979250726871</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>2486</v>
+        <v>3008</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>一詮</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>351.0225998798653</v>
+        <v>351.7129569569793</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>201</v>
+        <v>6175</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,49 +7071,49 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>31.30022971054279</v>
+        <v>45.96235812293177</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>22.76016173821296</v>
+        <v>13.78237983254298</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.7609791259070073</v>
+        <v>0.6587573071978704</v>
       </c>
       <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M125" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-3.019720008866019</v>
+        <v>-99.37802425919395</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>2704</v>
+        <v>2486</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>國賓</t>
+          <t>一詮</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>348.7322205835328</v>
+        <v>351.0225998798653</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>44.6</v>
+        <v>201</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>43.41097536449044</v>
+        <v>31.30022974262661</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>9.320404026477583</v>
+        <v>22.7601620306583</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.7210475739300293</v>
+        <v>0.7609791259070073</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.03819265610347874</v>
+        <v>-3.019720009930274</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>2903</v>
+        <v>2704</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>遠百</t>
+          <t>國賓</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>347.6411240685391</v>
+        <v>348.7322205835328</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>22.05</v>
+        <v>44.6</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>47.46687754630697</v>
+        <v>43.4109753529357</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>13.34939001367006</v>
+        <v>9.320403984539277</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.3716251344584184</v>
+        <v>0.7210475739300293</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.002308114908486274</v>
+        <v>-0.03819265614242087</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>2705</v>
+        <v>2903</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>遠百</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>347.0666811873618</v>
+        <v>347.6411240685391</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>14.95</v>
+        <v>22.05</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>31.37275804626556</v>
+        <v>47.46687756665811</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>33.71859709648081</v>
+        <v>13.34938997251889</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>1.147283405493178</v>
+        <v>0.3716251344584184</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.01177867937297417</v>
+        <v>-0.002308114921464646</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending, stronger_than_market</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>2458</v>
+        <v>2705</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>340.1972256837566</v>
+        <v>347.0666811873618</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>130</v>
+        <v>14.95</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>42.15339490787667</v>
+        <v>31.37275800372409</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>20.72654245144415</v>
+        <v>33.7185971328695</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.6299392841426403</v>
+        <v>1.147283405493178</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.1503423136319096</v>
+        <v>0.01177867937297417</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>2535</v>
+        <v>2458</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>338.7279337865272</v>
+        <v>340.1972256837566</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>89.2</v>
+        <v>130</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,16 +7336,16 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>49.10992086037169</v>
+        <v>42.15339534976031</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>11.00466306696763</v>
+        <v>20.72654248518852</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.744336204905148</v>
+        <v>0.6299392841426403</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.08268817726443825</v>
+        <v>-0.1503423136319096</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, stronger_than_market, kd_golden_cross</t>
+          <t>avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>2640</v>
+        <v>2535</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>336.898507506295</v>
+        <v>338.7279337865271</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>147.5</v>
+        <v>89.2</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,16 +7389,16 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>33.95606869623801</v>
+        <v>49.10992091921439</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>19.65033864988764</v>
+        <v>11.00466325597341</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>4.507653730532818</v>
+        <v>0.744336204905148</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" s="2" t="n">
         <v>0</v>
@@ -7407,31 +7407,31 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.8662375701098605</v>
+        <v>-0.08268817744614115</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>2636</v>
+        <v>2640</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>台驊控股</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>331.0761427548999</v>
+        <v>336.898507506295</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>70.3</v>
+        <v>147.5</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,16 +7442,16 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>46.26471672093957</v>
+        <v>33.95606871733523</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>21.94015945935967</v>
+        <v>19.65033871663909</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.6258881668004848</v>
+        <v>4.507653730532818</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L132" s="2" t="n">
         <v>0</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-0.1951314197989863</v>
+        <v>-0.8662375701098605</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>2464</v>
+        <v>2636</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>盟立</t>
+          <t>台驊控股</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>324.3734949065145</v>
+        <v>331.0761427548999</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>161</v>
+        <v>70.3</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,49 +7495,49 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>34.90317440238742</v>
+        <v>46.26471674936219</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>15.4557891219175</v>
+        <v>21.94015958125172</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.6565710287312002</v>
+        <v>0.6258881668004848</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L133" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M133" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-3.001775843807708</v>
+        <v>-0.1951314199547214</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>3049</v>
+        <v>2464</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>精金</t>
+          <t>盟立</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>320.7810735203233</v>
+        <v>324.3734949065143</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>11.5</v>
+        <v>161</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,49 +7548,49 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>40.33738739874945</v>
+        <v>34.90317445982744</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>12.69121812935327</v>
+        <v>15.45578908541229</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.6438098816768137</v>
+        <v>0.6565710287312002</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L134" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-0.0720848851977253</v>
+        <v>-3.001775843989412</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, foreign_buy_3d, stronger_than_market</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>2852</v>
+        <v>3049</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>第一保</t>
+          <t>精金</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>319.3758123966956</v>
+        <v>320.7810735203233</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>27.85</v>
+        <v>11.5</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,16 +7601,16 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>48.78337293561559</v>
+        <v>40.33738741777264</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>13.13478715604885</v>
+        <v>12.69121814700962</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.4336194881723438</v>
+        <v>0.6438098816768137</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L135" s="2" t="n">
         <v>0</v>
@@ -7619,31 +7619,31 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>0.001358384321346517</v>
+        <v>-0.07208488523406575</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>2923</v>
+        <v>2852</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>鼎固-KY</t>
+          <t>第一保</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>319.0032150597176</v>
+        <v>319.3758123966957</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>24.45</v>
+        <v>27.85</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,16 +7654,16 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>46.98536343446177</v>
+        <v>48.78337293561559</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>9.361723837469846</v>
+        <v>13.13478716827785</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.7008191880634951</v>
+        <v>0.4336194881723438</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L136" s="2" t="n">
         <v>0</v>
@@ -7672,31 +7672,31 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.05563271241527257</v>
+        <v>0.00135838433432525</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>3073</v>
+        <v>2923</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>天方能源</t>
+          <t>鼎固-KY</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>315.8262163117201</v>
+        <v>319.0032150597175</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>20.2</v>
+        <v>24.45</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,16 +7707,16 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>41.1817822416846</v>
+        <v>46.98536351028262</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>23.16999116258576</v>
+        <v>9.361723858754344</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>1.666493268690568</v>
+        <v>0.7008191880634951</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L137" s="2" t="n">
         <v>0</v>
@@ -7725,31 +7725,31 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>0.005617954430991862</v>
+        <v>0.05563271231144262</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>volume_break, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>2477</v>
+        <v>3073</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>美隆電</t>
+          <t>天方能源</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>314.8481426365175</v>
+        <v>315.8262163117213</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>22.2</v>
+        <v>20.2</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,16 +7760,16 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>44.50643992112921</v>
+        <v>41.18178212825982</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>27.03685583457092</v>
+        <v>23.1699912176212</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>1.393532787778166</v>
+        <v>1.666493268690568</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L138" s="2" t="n">
         <v>0</v>
@@ -7778,31 +7778,31 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>-0.07150740670452055</v>
+        <v>0.005617954560779598</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>3081</v>
+        <v>2477</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>美隆電</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>311.8866643891915</v>
+        <v>314.8481426365176</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>2375</v>
+        <v>22.2</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -7813,16 +7813,16 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>39.3187003824582</v>
+        <v>44.50644029818359</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>16.45600850026751</v>
+        <v>27.0368560118699</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>1.112614675244695</v>
+        <v>1.393532787778166</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L139" s="2" t="n">
         <v>0</v>
@@ -7831,31 +7831,31 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>-51.13296653834718</v>
+        <v>-0.07150740708090406</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>2509</v>
+        <v>3081</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>全坤建</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>310.9196580101558</v>
+        <v>311.8866643891916</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>13.05</v>
+        <v>2375</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -7866,13 +7866,13 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>29.79336387442063</v>
+        <v>39.31870039689782</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>26.50168138423483</v>
+        <v>16.45600864502109</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.6891350105669644</v>
+        <v>1.112614675244695</v>
       </c>
       <c r="K140" s="2" t="n">
         <v>0</v>
@@ -7884,31 +7884,31 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-0.05104369895253319</v>
+        <v>-51.13296654379819</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>3040</v>
+        <v>2509</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>遠見</t>
+          <t>全坤建</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>310.4449801876943</v>
+        <v>310.9196580101554</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>29.7</v>
+        <v>13.05</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7919,13 +7919,13 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>24.92037676285825</v>
+        <v>29.79336397825612</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>22.12926973852859</v>
+        <v>26.50168138423483</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.5394939092582285</v>
+        <v>0.6891350105669644</v>
       </c>
       <c r="K141" s="2" t="n">
         <v>0</v>
@@ -7937,7 +7937,7 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>-0.1883554855830676</v>
+        <v>-0.05104369893955318</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
@@ -7947,21 +7947,21 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>2911</v>
+        <v>3040</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>麗嬰房</t>
+          <t>遠見</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>309.1276882473193</v>
+        <v>310.4449801876943</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>5.99</v>
+        <v>29.7</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7972,13 +7972,13 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>42.65031857652167</v>
+        <v>24.92037700340302</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>13.0418301887947</v>
+        <v>22.12926968164967</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.5556022504746785</v>
+        <v>0.5394939092582285</v>
       </c>
       <c r="K142" s="2" t="n">
         <v>0</v>
@@ -7990,31 +7990,31 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>0.02917627463110925</v>
+        <v>-0.1883554859724312</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>2472</v>
+        <v>2911</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>麗嬰房</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>306.5833458075281</v>
+        <v>309.1276882473193</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>202.5</v>
+        <v>5.99</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -8025,13 +8025,13 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>37.4686433232033</v>
+        <v>42.65031856486448</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>16.47024255337333</v>
+        <v>13.04183025208686</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.7362759507559887</v>
+        <v>0.5556022504746785</v>
       </c>
       <c r="K143" s="2" t="n">
         <v>0</v>
@@ -8043,31 +8043,31 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>-2.499100635424608</v>
+        <v>0.02917627463370506</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>2505</v>
+        <v>2472</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>國揚</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>304.3141283141986</v>
+        <v>306.583345807528</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>17.65</v>
+        <v>202.5</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -8078,16 +8078,16 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>54.1107261811481</v>
+        <v>37.46864334229223</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>30.0136364346169</v>
+        <v>16.47024273729877</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.4636672827973987</v>
+        <v>0.7362759507559887</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L144" s="2" t="n">
         <v>0</v>
@@ -8096,31 +8096,31 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>0.07450240091926782</v>
+        <v>-2.499100636255259</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>2536</v>
+        <v>2505</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>宏普</t>
+          <t>國揚</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>304.2618008475396</v>
+        <v>304.3141283141986</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>18.25</v>
+        <v>17.65</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -8131,16 +8131,16 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>38.13450924855153</v>
+        <v>54.1107262303526</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>14.62620663667541</v>
+        <v>30.01363641578784</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.1576787177624713</v>
+        <v>0.4636672827973987</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L145" s="2" t="n">
         <v>0</v>
@@ -8149,31 +8149,31 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>0.006727821852771931</v>
+        <v>0.07450240088033183</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, avoid_chase, hist_turn_positive, stronger_than_market</t>
+          <t>avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>3071</v>
+        <v>2536</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>協禧</t>
+          <t>宏普</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v/>
       </c>
       <c r="D146" s="2" t="n">
-        <v>298.104358470278</v>
+        <v>304.2618008475396</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>21.7</v>
+        <v>18.25</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -8184,16 +8184,16 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>28.47202136371891</v>
+        <v>38.13450927348829</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>38.17029013841321</v>
+        <v>14.62620669631222</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.7064990804793668</v>
+        <v>0.1576787177624713</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L146" s="2" t="n">
         <v>0</v>
@@ -8202,31 +8202,31 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>-0.006367604298677776</v>
+        <v>0.00672782186575055</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending, stronger_than_market</t>
+          <t>macd_golden_cross, avoid_chase, hist_turn_positive, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>3048</v>
+        <v>3071</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>益登</t>
+          <t>協禧</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v/>
       </c>
       <c r="D147" s="2" t="n">
-        <v>294.7912317385558</v>
+        <v>298.1043584702778</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>52.8</v>
+        <v>21.7</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -8237,13 +8237,13 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>46.78619363426009</v>
+        <v>28.47202098306909</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>16.81437216487053</v>
+        <v>38.17029030474674</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.7356774618727012</v>
+        <v>0.7064990804793668</v>
       </c>
       <c r="K147" s="2" t="n">
         <v>0</v>
@@ -8255,31 +8255,31 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>-0.01929962276392638</v>
+        <v>-0.006367604103995173</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>2838</v>
+        <v>3048</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>聯邦銀</t>
+          <t>益登</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v/>
       </c>
       <c r="D148" s="2" t="n">
-        <v>292.6483159539847</v>
+        <v>294.7912317385557</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>20.5</v>
+        <v>52.8</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -8290,49 +8290,49 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>48.04578828093745</v>
+        <v>46.78619358041447</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>12.92841910640919</v>
+        <v>16.81437217199812</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.6526902498242347</v>
+        <v>0.7356774618727012</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L148" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M148" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-0.00927130962561698</v>
+        <v>-0.01929962177754729</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>2616</v>
+        <v>2838</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>山隆</t>
+          <t>聯邦銀</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v/>
       </c>
       <c r="D149" s="2" t="n">
-        <v>292.4420044404857</v>
+        <v>292.6483159539847</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>13.05</v>
+        <v>20.5</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -8343,49 +8343,49 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>31.1196535260663</v>
+        <v>48.0457881643639</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>16.9798251926336</v>
+        <v>12.92841900142494</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>1.236260956402194</v>
+        <v>0.6526902498242347</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L149" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M149" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>-0.004360921398146596</v>
+        <v>-0.009271309547742662</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>2506</v>
+        <v>2616</v>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>太設</t>
+          <t>山隆</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
         <v/>
       </c>
       <c r="D150" s="2" t="n">
-        <v>290.2952979601952</v>
+        <v>292.4420044404857</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>8.4</v>
+        <v>13.05</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -8396,16 +8396,16 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>44.77113492133223</v>
+        <v>31.11965366107057</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>14.83833214625859</v>
+        <v>16.9798251926336</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.5362131154300699</v>
+        <v>1.236260956402194</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L150" s="2" t="n">
         <v>0</v>
@@ -8414,7 +8414,7 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>0.007350385665473767</v>
+        <v>-0.004360921424105844</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
@@ -8424,21 +8424,21 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>3025</v>
+        <v>2506</v>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>星通</t>
+          <t>太設</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v/>
       </c>
       <c r="D151" s="2" t="n">
-        <v>290.1171886549899</v>
+        <v>290.2952979601952</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>54</v>
+        <v>8.4</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -8449,16 +8449,16 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>47.6715832891476</v>
+        <v>44.77113506532987</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>31.07176739959129</v>
+        <v>14.83833217707708</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>0.3096566220677379</v>
+        <v>0.5362131154300699</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L151" s="2" t="n">
         <v>0</v>
@@ -8467,31 +8467,31 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>-0.1998657327838439</v>
+        <v>0.007350385642111268</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>3019</v>
+        <v>3025</v>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>亞光</t>
+          <t>星通</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
         <v/>
       </c>
       <c r="D152" s="2" t="n">
-        <v>287.1922210333402</v>
+        <v>290.117188654996</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>129.5</v>
+        <v>54</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
@@ -8502,13 +8502,13 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>39.35739861452203</v>
+        <v>47.671583319733</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>12.38241382435498</v>
+        <v>31.07176765520155</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>0.6994731586771628</v>
+        <v>0.3096566220677379</v>
       </c>
       <c r="K152" s="2" t="n">
         <v>0</v>
@@ -8520,31 +8520,31 @@
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>-0.7093332767325746</v>
+        <v>-0.1998657333549062</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>2493</v>
+        <v>3019</v>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>揚博</t>
+          <t>亞光</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
         <v/>
       </c>
       <c r="D153" s="2" t="n">
-        <v>285.0482151981204</v>
+        <v>287.1922210333402</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>190</v>
+        <v>129.5</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -8555,49 +8555,49 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>46.19626508038896</v>
+        <v>39.3573987170837</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>13.87327472589222</v>
+        <v>12.3824139775034</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>1.138805565488487</v>
+        <v>0.6994731586771628</v>
       </c>
       <c r="K153" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L153" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M153" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>-2.066845913570569</v>
+        <v>-0.7093332781602362</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>吉祥全</t>
+          <t>揚博</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
         <v/>
       </c>
       <c r="D154" s="2" t="n">
-        <v>284.8875260529662</v>
+        <v>285.0482151981205</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>35.3</v>
+        <v>190</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -8608,49 +8608,49 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>40.59893213544307</v>
+        <v>46.19626517597657</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>18.26385831686281</v>
+        <v>13.87327494046911</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>0.7578812105384907</v>
+        <v>1.138805565488487</v>
       </c>
       <c r="K154" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L154" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M154" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>-0.3617820661809064</v>
+        <v>-2.066845917593995</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>3024</v>
+        <v>2491</v>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>憶聲</t>
+          <t>吉祥全</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v/>
       </c>
       <c r="D155" s="2" t="n">
-        <v>282.4247659315035</v>
+        <v>284.8875260529662</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>13.1</v>
+        <v>35.3</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -8661,16 +8661,16 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>35.80290077888132</v>
+        <v>40.59893215530693</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>16.78057246838671</v>
+        <v>18.26385838011461</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.5639635384076626</v>
+        <v>0.7578812105384907</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L155" s="2" t="n">
         <v>0</v>
@@ -8679,31 +8679,31 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>-0.1071257817772062</v>
+        <v>-0.3617820663626137</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>2496</v>
+        <v>3024</v>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>卓越</t>
+          <t>憶聲</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
         <v/>
       </c>
       <c r="D156" s="2" t="n">
-        <v>280.9017236308257</v>
+        <v>282.4247659315035</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>54.5</v>
+        <v>13.1</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -8714,16 +8714,16 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>40.88434874922875</v>
+        <v>35.8029008464582</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>20.52121052759555</v>
+        <v>16.78057255485419</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.4980778349485268</v>
+        <v>0.5639635384076626</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L156" s="2" t="n">
         <v>0</v>
@@ -8732,31 +8732,31 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>0.03109437766753809</v>
+        <v>-0.1071257818291205</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>2538</v>
+        <v>2496</v>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>基泰</t>
+          <t>卓越</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v/>
       </c>
       <c r="D157" s="2" t="n">
-        <v>277.3249504467603</v>
+        <v>280.9017236308256</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>8.65</v>
+        <v>54.5</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -8767,16 +8767,16 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>42.6463173221788</v>
+        <v>40.88434887201726</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>18.40229511619449</v>
+        <v>20.52121050859692</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>0.5712335199885328</v>
+        <v>0.4980778349485268</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L157" s="2" t="n">
         <v>0</v>
@@ -8785,31 +8785,31 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>-0.00520425045042068</v>
+        <v>0.03109437756371164</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, stronger_than_market, kd_golden_cross</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>2849</v>
+        <v>2538</v>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>安泰銀</t>
+          <t>基泰</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v/>
       </c>
       <c r="D158" s="2" t="n">
-        <v>276.8023891243168</v>
+        <v>277.3249504467603</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>15.4</v>
+        <v>8.65</v>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
@@ -8820,13 +8820,13 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>48.18687765903453</v>
+        <v>42.6463173221788</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>17.01715756025502</v>
+        <v>18.40229509550641</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>0.7700800749447951</v>
+        <v>0.5712335199885328</v>
       </c>
       <c r="K158" s="2" t="n">
         <v>1</v>
@@ -8838,31 +8838,31 @@
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>-0.06242731584866047</v>
+        <v>-0.00520425045042068</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>2498</v>
+        <v>2849</v>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>宏達電</t>
+          <t>安泰銀</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
         <v/>
       </c>
       <c r="D159" s="2" t="n">
-        <v>275.2654811912809</v>
+        <v>276.8023891243168</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>39.75</v>
+        <v>15.4</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -8873,16 +8873,16 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>42.12327322023452</v>
+        <v>48.18687767363646</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>17.42999700921373</v>
+        <v>17.01715756025502</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>0.5067630713733464</v>
+        <v>0.7700800749447951</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L159" s="2" t="n">
         <v>0</v>
@@ -8891,31 +8891,31 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>-0.2251745782931321</v>
+        <v>-0.06242731586164017</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, liquidity_ok, stronger_than_market</t>
+          <t>ema60_gt_ema120, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>3038</v>
+        <v>2498</v>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>全台</t>
+          <t>宏達電</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
         <v/>
       </c>
       <c r="D160" s="2" t="n">
-        <v>272.8714724102375</v>
+        <v>275.2654811912806</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>20.1</v>
+        <v>39.75</v>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
@@ -8926,13 +8926,13 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>42.72964119549136</v>
+        <v>42.12327264569419</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>20.4307354910276</v>
+        <v>17.42999733926875</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>0.8071419991133283</v>
+        <v>0.5067630713733464</v>
       </c>
       <c r="K160" s="2" t="n">
         <v>0</v>
@@ -8944,31 +8944,31 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>-0.02832837357291578</v>
+        <v>-0.2251745776441927</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending, stronger_than_market</t>
+          <t>avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>2712</v>
+        <v>3038</v>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>遠雄來</t>
+          <t>全台</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
         <v/>
       </c>
       <c r="D161" s="2" t="n">
-        <v>271.8641752165652</v>
+        <v>272.8714724102363</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>13.3</v>
+        <v>20.1</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -8979,16 +8979,16 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>45.28411915481878</v>
+        <v>42.72964132358595</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>15.52215861587491</v>
+        <v>20.43073560220833</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>0.3085982146732447</v>
+        <v>0.8071419991133283</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L161" s="2" t="n">
         <v>0</v>
@@ -8997,31 +8997,31 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>0.02260202218019172</v>
+        <v>-0.02832837366376802</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>2706</v>
+        <v>2712</v>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>第一店</t>
+          <t>遠雄來</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
         <v/>
       </c>
       <c r="D162" s="2" t="n">
-        <v>271.7964621146773</v>
+        <v>271.8641752165652</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>12.05</v>
+        <v>13.3</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -9032,16 +9032,16 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>35.11584317782972</v>
+        <v>45.28411921492818</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>15.91601444431932</v>
+        <v>15.5221585796846</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>0.5505321238124874</v>
+        <v>0.3085982146732447</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L162" s="2" t="n">
         <v>0</v>
@@ -9050,31 +9050,31 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>0.003333684351434177</v>
+        <v>0.02260202212827608</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>3058</v>
+        <v>2706</v>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>立德</t>
+          <t>第一店</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v/>
       </c>
       <c r="D163" s="2" t="n">
-        <v>271.5830680077875</v>
+        <v>271.7964621146774</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>8.02</v>
+        <v>12.05</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -9085,13 +9085,13 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>42.49082789397902</v>
+        <v>35.11584324334957</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>26.7880449204014</v>
+        <v>15.91601424236665</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>0.863741978588675</v>
+        <v>0.5505321238124874</v>
       </c>
       <c r="K163" s="2" t="n">
         <v>0</v>
@@ -9103,31 +9103,31 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>-0.03573637592389703</v>
+        <v>0.003333684338455122</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending, obv_uptrend</t>
+          <t>avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>3085</v>
+        <v>3058</v>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>新零售</t>
+          <t>立德</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v/>
       </c>
       <c r="D164" s="2" t="n">
-        <v>271.5320565289348</v>
+        <v>271.5830680077876</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>0</v>
+        <v>8.02</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -9138,13 +9138,13 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>45.60923967334001</v>
+        <v>42.49082807179081</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>8.083638435767609</v>
+        <v>26.78804498581907</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>0.07304712403963563</v>
+        <v>0.863741978588675</v>
       </c>
       <c r="K164" s="2" t="n">
         <v>0</v>
@@ -9156,31 +9156,31 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>-0.354593953989064</v>
+        <v>-0.03573637602772788</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>3003</v>
+        <v>3085</v>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>健和興</t>
+          <t>新零售</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v/>
       </c>
       <c r="D165" s="2" t="n">
-        <v>267.0198046999714</v>
+        <v>271.5320565289347</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>54.3</v>
+        <v>0</v>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
@@ -9191,13 +9191,13 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>31.22291467056547</v>
+        <v>45.6092396632764</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>22.79551989503455</v>
+        <v>8.083638410794652</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>1.256775495738611</v>
+        <v>0.07304712403963563</v>
       </c>
       <c r="K165" s="2" t="n">
         <v>0</v>
@@ -9209,31 +9209,31 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>-0.1886214283615586</v>
+        <v>-0.3545939540714455</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>2722</v>
+        <v>3003</v>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>夏都</t>
+          <t>健和興</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v/>
       </c>
       <c r="D166" s="2" t="n">
-        <v>259.9421763819297</v>
+        <v>267.0198046999714</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>19.95</v>
+        <v>54.3</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -9244,13 +9244,13 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>22.4451238856963</v>
+        <v>31.22291470919031</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>14.81479781355013</v>
+        <v>22.79551991477957</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>2.202924728194796</v>
+        <v>1.256775495738611</v>
       </c>
       <c r="K166" s="2" t="n">
         <v>0</v>
@@ -9262,31 +9262,31 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>-0.1078303467725423</v>
+        <v>-0.1886214288028349</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>volume_break, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>3046</v>
+        <v>2722</v>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>建碁</t>
+          <t>夏都</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v/>
       </c>
       <c r="D167" s="2" t="n">
-        <v>259.7938201143247</v>
+        <v>259.9421763819296</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>51.1</v>
+        <v>19.95</v>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
@@ -9297,16 +9297,16 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>36.69770618141355</v>
+        <v>22.44512315373683</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>19.12110350929161</v>
+        <v>14.81479780793756</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>0.8464610782254472</v>
+        <v>2.202924728194796</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L167" s="2" t="n">
         <v>0</v>
@@ -9315,31 +9315,31 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>-0.05582737564738338</v>
+        <v>-0.1078303464999892</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, stronger_than_market</t>
+          <t>volume_break, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>3060</v>
+        <v>3046</v>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>銘異</t>
+          <t>建碁</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
         <v/>
       </c>
       <c r="D168" s="2" t="n">
-        <v>253.6303089698365</v>
+        <v>259.7938201143246</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>26.75</v>
+        <v>51.1</v>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
@@ -9350,16 +9350,16 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>42.51043323184146</v>
+        <v>36.69770628004311</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>17.3419516307062</v>
+        <v>19.12110368416399</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>0.5219349141117053</v>
+        <v>0.8464610782254472</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L168" s="2" t="n">
         <v>0</v>
@@ -9368,31 +9368,31 @@
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>-0.137055340935868</v>
+        <v>-0.05582737604972032</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>3041</v>
+        <v>3060</v>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>揚智</t>
+          <t>銘異</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
         <v/>
       </c>
       <c r="D169" s="2" t="n">
-        <v>251.1022426870902</v>
+        <v>253.6303089698365</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>23.15</v>
+        <v>26.75</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
@@ -9403,13 +9403,13 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>44.46286739310879</v>
+        <v>42.51043329389953</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>20.89076546087951</v>
+        <v>17.34195182121777</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>0.6154892070149406</v>
+        <v>0.5219349141117053</v>
       </c>
       <c r="K169" s="2" t="n">
         <v>0</v>
@@ -9421,31 +9421,31 @@
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>-0.1573588320274415</v>
+        <v>-0.1370553411435285</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending, mfi_strong</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>2832</v>
+        <v>3041</v>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>台產</t>
+          <t>揚智</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
         <v/>
       </c>
       <c r="D170" s="2" t="n">
-        <v>244.6192460010134</v>
+        <v>251.1022426870903</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>55.7</v>
+        <v>23.15</v>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
@@ -9456,16 +9456,16 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>37.04723287916359</v>
+        <v>44.46286740615979</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>13.25179515643176</v>
+        <v>20.89076563196143</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>1.464353610775058</v>
+        <v>0.6154892070149406</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L170" s="2" t="n">
         <v>0</v>
@@ -9474,31 +9474,31 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>-0.1112275737468597</v>
+        <v>-0.1573588321442507</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, kd_golden_cross</t>
+          <t>avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>2461</v>
+        <v>2832</v>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>光群雷</t>
+          <t>台產</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
         <v/>
       </c>
       <c r="D171" s="2" t="n">
-        <v>244.4406384271732</v>
+        <v>244.6192460010134</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>16.5</v>
+        <v>55.7</v>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
@@ -9509,13 +9509,13 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>38.51308083704408</v>
+        <v>37.04723301940401</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>18.4071597895214</v>
+        <v>13.25179518609877</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>0.3244232281529167</v>
+        <v>1.464353610775058</v>
       </c>
       <c r="K171" s="2" t="n">
         <v>1</v>
@@ -9527,31 +9527,31 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>-0.02202302395081923</v>
+        <v>-0.1112275739025583</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>2904</v>
+        <v>2461</v>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>匯僑</t>
+          <t>光群雷</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
         <v/>
       </c>
       <c r="D172" s="2" t="n">
-        <v>242.1533977469897</v>
+        <v>244.4406384271732</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>12.55</v>
+        <v>16.5</v>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
@@ -9562,16 +9562,16 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>44.68923777548858</v>
+        <v>38.51308094937624</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>18.20686102021175</v>
+        <v>18.40715959498293</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>0.3148614968311614</v>
+        <v>0.3244232281529167</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L172" s="2" t="n">
         <v>0</v>
@@ -9580,31 +9580,31 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>0.008548302109033235</v>
+        <v>-0.02202302400273082</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>3042</v>
+        <v>2904</v>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>匯僑</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
         <v/>
       </c>
       <c r="D173" s="2" t="n">
-        <v>241.0270406210976</v>
+        <v>242.1533977469897</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>169.5</v>
+        <v>12.55</v>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
@@ -9615,13 +9615,13 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>37.24393444059707</v>
+        <v>44.6892376664519</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>18.11233650177852</v>
+        <v>18.20686106443848</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>0.6326361004628215</v>
+        <v>0.3148614968311614</v>
       </c>
       <c r="K173" s="2" t="n">
         <v>0</v>
@@ -9633,31 +9633,31 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>-4.709869350741664</v>
+        <v>0.008548302122010659</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>2450</v>
+        <v>3042</v>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>神腦</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
         <v/>
       </c>
       <c r="D174" s="2" t="n">
-        <v>240.3179938306961</v>
+        <v>241.0270406210976</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>28.05</v>
+        <v>169.5</v>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
@@ -9668,16 +9668,16 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>41.38079251073606</v>
+        <v>37.24393446335813</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>13.62126115478578</v>
+        <v>18.11233668192828</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>1.42699443262022</v>
+        <v>0.6326361004628215</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L174" s="2" t="n">
         <v>0</v>
@@ -9686,31 +9686,31 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-0.01038878798162693</v>
+        <v>-4.7098693513906</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>2748</v>
+        <v>2450</v>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>雲品</t>
+          <t>神腦</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
         <v/>
       </c>
       <c r="D175" s="2" t="n">
-        <v>240.150314730332</v>
+        <v>240.3179938306961</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>37.9</v>
+        <v>28.05</v>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
@@ -9721,16 +9721,16 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>33.66191974713615</v>
+        <v>41.38079259369658</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>19.22685155009054</v>
+        <v>13.62126115478578</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>1.181382082710356</v>
+        <v>1.42699443262022</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L175" s="2" t="n">
         <v>0</v>
@@ -9739,7 +9739,7 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>-0.07602936351756642</v>
+        <v>-0.01038878800758734</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
@@ -9749,21 +9749,21 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>2630</v>
+        <v>2748</v>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>亞航</t>
+          <t>雲品</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
         <v/>
       </c>
       <c r="D176" s="2" t="n">
-        <v>239.817384243555</v>
+        <v>240.1503147303318</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>42.35</v>
+        <v>37.9</v>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
@@ -9774,16 +9774,16 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>28.9482570475754</v>
+        <v>33.66191968225733</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>21.63508660441764</v>
+        <v>19.22685155149927</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>0.6976685868789249</v>
+        <v>1.181382082710356</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L176" s="2" t="n">
         <v>0</v>
@@ -9792,31 +9792,31 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>-0.187596188196741</v>
+        <v>-0.07602936351756642</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>3088</v>
+        <v>2630</v>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>艾訊</t>
+          <t>亞航</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
         <v/>
       </c>
       <c r="D177" s="2" t="n">
-        <v>228.614359736939</v>
+        <v>239.8173842435572</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>117</v>
+        <v>42.35</v>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
@@ -9827,16 +9827,16 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>31.77941280867429</v>
+        <v>28.94825650379946</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>19.47919834722765</v>
+        <v>21.63508673341572</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>0.587562598346256</v>
+        <v>0.6976685868789249</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L177" s="2" t="n">
         <v>0</v>
@@ -9845,31 +9845,31 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>-1.547193549423804</v>
+        <v>-0.1875961874180234</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>2642</v>
+        <v>3088</v>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>宅配通</t>
+          <t>艾訊</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
         <v/>
       </c>
       <c r="D178" s="2" t="n">
-        <v>228.2374235031967</v>
+        <v>228.614359736939</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
@@ -9880,13 +9880,13 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>37.09061338042571</v>
+        <v>31.77941283232781</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>13.88209851700905</v>
+        <v>19.47919841181175</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>3.939866485233143</v>
+        <v>0.587562598346256</v>
       </c>
       <c r="K178" s="2" t="n">
         <v>0</v>
@@ -9898,31 +9898,31 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>-0.02465691946118859</v>
+        <v>-1.54719354991699</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
-          <t>volume_break, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>3090</v>
+        <v>2642</v>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>日電貿</t>
+          <t>宅配通</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
         <v/>
       </c>
       <c r="D179" s="2" t="n">
-        <v>227.1545235268532</v>
+        <v>228.2374235031965</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>156.5</v>
+        <v>20</v>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
@@ -9933,49 +9933,49 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>41.70378716877016</v>
+        <v>37.09061351554261</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>13.23085032749237</v>
+        <v>13.88209853251779</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>0.7129140251667055</v>
+        <v>3.939866485233143</v>
       </c>
       <c r="K179" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L179" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M179" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>-1.412324572659222</v>
+        <v>-0.02465691947416643</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
+          <t>volume_break, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>2739</v>
+        <v>3090</v>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>寒舍</t>
+          <t>日電貿</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
         <v/>
       </c>
       <c r="D180" s="2" t="n">
-        <v>222.9658857162466</v>
+        <v>227.1545235268533</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>34.7</v>
+        <v>156.5</v>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
@@ -9986,49 +9986,49 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>26.40896606260804</v>
+        <v>41.70378718266276</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>17.36920757740215</v>
+        <v>13.23085047715677</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>3.50443053353448</v>
+        <v>0.7129140251667055</v>
       </c>
       <c r="K180" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L180" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M180" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>-0.1164938348509173</v>
+        <v>-1.412324573022615</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, avoid_chase</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>2467</v>
+        <v>2739</v>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>寒舍</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
         <v/>
       </c>
       <c r="D181" s="2" t="n">
-        <v>222.5842119254856</v>
+        <v>222.9658857162466</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v>452</v>
+        <v>34.7</v>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
@@ -10039,13 +10039,13 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>30.04866702017742</v>
+        <v>26.40896598403125</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>16.46876587134873</v>
+        <v>17.36920756451368</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>0.839323304081886</v>
+        <v>3.50443053353448</v>
       </c>
       <c r="K181" s="2" t="n">
         <v>0</v>
@@ -10057,31 +10057,31 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>-10.01004099660276</v>
+        <v>-0.1164938347989992</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, volume_break, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>3122</v>
+        <v>2467</v>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>笙泉</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
         <v/>
       </c>
       <c r="D182" s="2" t="n">
-        <v>220.8383715041484</v>
+        <v>222.5842119254837</v>
       </c>
       <c r="E182" s="2" t="n">
-        <v>22.3</v>
+        <v>452</v>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
@@ -10092,13 +10092,13 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>32.25510641440607</v>
+        <v>30.04866702802165</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>18.52595011639518</v>
+        <v>16.46876598901444</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>2.211570275507906</v>
+        <v>0.839323304081886</v>
       </c>
       <c r="K182" s="2" t="n">
         <v>0</v>
@@ -10110,31 +10110,31 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>-0.08223432861358349</v>
+        <v>-10.01004099880906</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
-          <t>volume_break, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>2528</v>
+        <v>3122</v>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>皇普</t>
+          <t>笙泉</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
         <v/>
       </c>
       <c r="D183" s="2" t="n">
-        <v>220.729032226335</v>
+        <v>220.8383715041343</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>17.15</v>
+        <v>22.3</v>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
@@ -10145,13 +10145,13 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>17.75984909960775</v>
+        <v>32.25510680188508</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>31.07741299240639</v>
+        <v>18.52595021963575</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>2.972903222633497</v>
+        <v>2.211570275507906</v>
       </c>
       <c r="K183" s="2" t="n">
         <v>0</v>
@@ -10163,31 +10163,31 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>-0.130212973940793</v>
+        <v>-0.08223432883422122</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
-          <t>volume_break, avoid_chase, adx_trending</t>
+          <t>volume_break, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>2530</v>
+        <v>2528</v>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>華建</t>
+          <t>皇普</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
         <v/>
       </c>
       <c r="D184" s="2" t="n">
-        <v>219.6636854026522</v>
+        <v>220.729032226335</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>19.95</v>
+        <v>17.15</v>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
@@ -10198,49 +10198,49 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>45.8004731309784</v>
+        <v>17.75984924523473</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>31.46990640379325</v>
+        <v>31.07741294659516</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>1.108296147948073</v>
+        <v>2.972903222633497</v>
       </c>
       <c r="K184" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L184" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M184" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>-0.05245571673735588</v>
+        <v>-0.1302129739667506</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>2812</v>
+        <v>2530</v>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t>華建</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
         <v/>
       </c>
       <c r="D185" s="2" t="n">
-        <v>217.8216943890513</v>
+        <v>219.6636854026522</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>18.6</v>
+        <v>19.95</v>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
@@ -10251,16 +10251,16 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>42.08954311135241</v>
+        <v>45.80047291734436</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>18.16381151822948</v>
+        <v>31.46990639360363</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>0.6861878957056818</v>
+        <v>1.108296147948073</v>
       </c>
       <c r="K185" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L185" s="2" t="n">
         <v>1</v>
@@ -10269,31 +10269,31 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>-0.002582285157170489</v>
+        <v>-0.05245571655565151</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, liquidity_ok, stronger_than_market</t>
+          <t>avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>2514</v>
+        <v>2812</v>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>龍邦</t>
+          <t>台中銀</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
         <v/>
       </c>
       <c r="D186" s="2" t="n">
-        <v>216.3831108853343</v>
+        <v>217.8216943890513</v>
       </c>
       <c r="E186" s="2" t="n">
-        <v>11.2</v>
+        <v>18.6</v>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
@@ -10304,49 +10304,49 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>39.07494380744679</v>
+        <v>42.08954314353697</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>32.03214080028618</v>
+        <v>18.16381154189959</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>0.4909209318008714</v>
+        <v>0.6861878957056818</v>
       </c>
       <c r="K186" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L186" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M186" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>0.006227244960230083</v>
+        <v>-0.002582285144193119</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending, stronger_than_market</t>
+          <t>avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>2707</v>
+        <v>2514</v>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>晶華</t>
+          <t>龍邦</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
         <v/>
       </c>
       <c r="D187" s="2" t="n">
-        <v>213.1178677009599</v>
+        <v>216.3831108853343</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>176</v>
+        <v>11.2</v>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
@@ -10357,13 +10357,13 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>44.89560336962526</v>
+        <v>39.07494390106422</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>17.91066811686871</v>
+        <v>32.03214066807779</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>1.04958952948967</v>
+        <v>0.4909209318008714</v>
       </c>
       <c r="K187" s="2" t="n">
         <v>1</v>
@@ -10375,31 +10375,31 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>0.1346724573143115</v>
+        <v>0.006227244921292119</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, stronger_than_market</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>3032</v>
+        <v>2707</v>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>偉訓</t>
+          <t>晶華</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
         <v/>
       </c>
       <c r="D188" s="2" t="n">
-        <v>212.3896173297958</v>
+        <v>213.1178677009598</v>
       </c>
       <c r="E188" s="2" t="n">
-        <v>72.5</v>
+        <v>176</v>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
@@ -10410,16 +10410,16 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>39.42819230076073</v>
+        <v>44.89560363370833</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>15.6560544504624</v>
+        <v>17.91066803733121</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>0.4375476809749864</v>
+        <v>1.04958952948967</v>
       </c>
       <c r="K188" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L188" s="2" t="n">
         <v>0</v>
@@ -10428,7 +10428,7 @@
         <v>-1</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>-0.4830976550317565</v>
+        <v>0.1346724570547306</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
@@ -10438,21 +10438,21 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>3078</v>
+        <v>3032</v>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>僑威</t>
+          <t>偉訓</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
         <v/>
       </c>
       <c r="D189" s="2" t="n">
-        <v>211.2907670297859</v>
+        <v>212.3896173297932</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>45.9</v>
+        <v>72.5</v>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
@@ -10463,13 +10463,13 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>42.44097546563243</v>
+        <v>39.42819275435444</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>17.66346623142548</v>
+        <v>15.65605421188746</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>1.450463641969027</v>
+        <v>0.4375476809749864</v>
       </c>
       <c r="K189" s="2" t="n">
         <v>0</v>
@@ -10481,31 +10481,31 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>0.1774723649282697</v>
+        <v>-0.4830976567189957</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>3057</v>
+        <v>3078</v>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>喬鼎</t>
+          <t>僑威</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
         <v/>
       </c>
       <c r="D190" s="2" t="n">
-        <v>209.8315123190274</v>
+        <v>211.2907670297856</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>14.15</v>
+        <v>45.9</v>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
@@ -10516,16 +10516,16 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>31.7621074906391</v>
+        <v>42.44097579066319</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>34.67127578161551</v>
+        <v>17.66346573348508</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>0.6739273895802724</v>
+        <v>1.450463641969027</v>
       </c>
       <c r="K190" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L190" s="2" t="n">
         <v>0</v>
@@ -10534,31 +10534,31 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>-0.08624705950678424</v>
+        <v>0.1774723637601874</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>2459</v>
+        <v>3057</v>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>敦吉</t>
+          <t>喬鼎</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
         <v/>
       </c>
       <c r="D191" s="2" t="n">
-        <v>208.5968595680793</v>
+        <v>209.8315123190274</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>63.4</v>
+        <v>14.15</v>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
@@ -10569,16 +10569,16 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>28.69402211546931</v>
+        <v>31.76210750871984</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>14.55528506955164</v>
+        <v>34.67127585504368</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>4.350607407176821</v>
+        <v>0.6739273895802724</v>
       </c>
       <c r="K191" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L191" s="2" t="n">
         <v>0</v>
@@ -10587,31 +10587,31 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>-0.07265330740698681</v>
+        <v>-0.08624705956445156</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
-          <t>volume_break, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>2495</v>
+        <v>2459</v>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>普安</t>
+          <t>敦吉</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
         <v/>
       </c>
       <c r="D192" s="2" t="n">
-        <v>203.877163329522</v>
+        <v>208.5968595680792</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>32.4</v>
+        <v>63.4</v>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
@@ -10622,13 +10622,13 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>26.20846419884681</v>
+        <v>28.69402212679135</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>28.77121551941259</v>
+        <v>14.55528510701873</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>0.7723333354227283</v>
+        <v>4.350607407176821</v>
       </c>
       <c r="K192" s="2" t="n">
         <v>0</v>
@@ -10640,31 +10640,31 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>-0.4847165093366042</v>
+        <v>-0.0726533075367734</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending</t>
+          <t>volume_break, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>2501</v>
+        <v>2495</v>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>國建</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
         <v/>
       </c>
       <c r="D193" s="2" t="n">
-        <v>201.1871465606487</v>
+        <v>203.8771633295405</v>
       </c>
       <c r="E193" s="2" t="n">
-        <v>20.45</v>
+        <v>32.4</v>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
@@ -10675,16 +10675,16 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>38.19266591229619</v>
+        <v>26.20846421932288</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>21.83322295855641</v>
+        <v>28.77121565246326</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>0.4454782689911795</v>
+        <v>0.7723333354227283</v>
       </c>
       <c r="K193" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L193" s="2" t="n">
         <v>0</v>
@@ -10693,31 +10693,31 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>0.04192334609818837</v>
+        <v>-0.4847165094663946</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending, stronger_than_market</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>2537</v>
+        <v>2501</v>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>聯上發</t>
+          <t>國建</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
         <v/>
       </c>
       <c r="D194" s="2" t="n">
-        <v>200.9609826828924</v>
+        <v>201.1871465606487</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>10.9</v>
+        <v>20.45</v>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
@@ -10728,16 +10728,16 @@
         <v>0</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>37.95553306598505</v>
+        <v>38.1926660926482</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>13.3874093740159</v>
+        <v>21.83322299530197</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>0.5492390088508141</v>
+        <v>0.4454782689911795</v>
       </c>
       <c r="K194" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L194" s="2" t="n">
         <v>0</v>
@@ -10746,31 +10746,31 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>-0.001646766788712339</v>
+        <v>0.04192334600733683</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, stronger_than_market</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>2929</v>
+        <v>2537</v>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>淘帝-KY</t>
+          <t>聯上發</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
         <v/>
       </c>
       <c r="D195" s="2" t="n">
-        <v>199.3919112956312</v>
+        <v>200.9609826828923</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>5.72</v>
+        <v>10.9</v>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
@@ -10781,13 +10781,13 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>46.7561862180325</v>
+        <v>37.9555333298274</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>12.48077362510243</v>
+        <v>13.38740956706532</v>
       </c>
       <c r="J195" s="2" t="n">
-        <v>0.8504493925605305</v>
+        <v>0.5492390088508141</v>
       </c>
       <c r="K195" s="2" t="n">
         <v>0</v>
@@ -10799,31 +10799,31 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>-0.004494334008990495</v>
+        <v>-0.001646766840627603</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>2906</v>
+        <v>2929</v>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>高林</t>
+          <t>淘帝-KY</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
         <v/>
       </c>
       <c r="D196" s="2" t="n">
-        <v>196.6038574498713</v>
+        <v>199.3919112956317</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>13.55</v>
+        <v>5.72</v>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
@@ -10834,16 +10834,16 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>46.40002839925641</v>
+        <v>46.75618630965812</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>17.2504024152632</v>
+        <v>12.48077372219393</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>0.4759424045309933</v>
+        <v>0.8504493925605305</v>
       </c>
       <c r="K196" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L196" s="2" t="n">
         <v>0</v>
@@ -10852,31 +10852,31 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>-0.006527888554959978</v>
+        <v>-0.004494334027160554</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>3051</v>
+        <v>2906</v>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>力特</t>
+          <t>高林</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
         <v/>
       </c>
       <c r="D197" s="2" t="n">
-        <v>195.249640779115</v>
+        <v>196.6038574498713</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>21.4</v>
+        <v>13.55</v>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
@@ -10887,16 +10887,16 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>41.87867320944135</v>
+        <v>46.40002847591983</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>15.95279237548262</v>
+        <v>17.25040218844584</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>1.142096699665133</v>
+        <v>0.4759424045309933</v>
       </c>
       <c r="K197" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L197" s="2" t="n">
         <v>0</v>
@@ -10905,31 +10905,31 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>-0.09790705633046903</v>
+        <v>-0.006527888606874602</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>2601</v>
+        <v>3051</v>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>益航</t>
+          <t>力特</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
         <v/>
       </c>
       <c r="D198" s="2" t="n">
-        <v>192.8450548958288</v>
+        <v>195.249640779115</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>5.93</v>
+        <v>21.4</v>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
@@ -10940,13 +10940,13 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>38.87834801590591</v>
+        <v>41.87867340504025</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>18.42256320584582</v>
+        <v>15.95279241144987</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>0.3839234692110819</v>
+        <v>1.142096699665133</v>
       </c>
       <c r="K198" s="2" t="n">
         <v>0</v>
@@ -10958,31 +10958,31 @@
         <v>-1</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>-0.002435727501882951</v>
+        <v>-0.097907056421321</v>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, stronger_than_market</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>2545</v>
+        <v>2601</v>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>皇翔</t>
+          <t>益航</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
         <v/>
       </c>
       <c r="D199" s="2" t="n">
-        <v>191.4944117793898</v>
+        <v>192.8450548958288</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>33.25</v>
+        <v>5.93</v>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
@@ -10993,13 +10993,13 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>41.007877302702</v>
+        <v>38.87834805795499</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>16.20458568781985</v>
+        <v>18.42256341733223</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>1.383064542000918</v>
+        <v>0.3839234692110819</v>
       </c>
       <c r="K199" s="2" t="n">
         <v>0</v>
@@ -11011,31 +11011,31 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>-0.1056516248369656</v>
+        <v>-0.002435727526597598</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>2482</v>
+        <v>2545</v>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>連宇</t>
+          <t>皇翔</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
         <v/>
       </c>
       <c r="D200" s="2" t="n">
-        <v>186.3796320064388</v>
+        <v>191.4944117793927</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>15.6</v>
+        <v>33.25</v>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
@@ -11046,13 +11046,13 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>39.88403388381952</v>
+        <v>41.0078774070325</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>12.22125781106013</v>
+        <v>16.20458577354</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>0.792643094580515</v>
+        <v>1.383064542000918</v>
       </c>
       <c r="K200" s="2" t="n">
         <v>0</v>
@@ -11064,31 +11064,31 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>-0.05493366168268612</v>
+        <v>-0.1056516250056882</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, stronger_than_market</t>
+          <t>avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>3043</v>
+        <v>2482</v>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>科風</t>
+          <t>連宇</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
         <v/>
       </c>
       <c r="D201" s="2" t="n">
-        <v>186.3733606055345</v>
+        <v>186.3796320064386</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>19.1</v>
+        <v>15.6</v>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
@@ -11099,13 +11099,13 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>32.33710608436867</v>
+        <v>39.88403382936222</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>21.36854127679817</v>
+        <v>12.22125793998997</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>0.8270837206060042</v>
+        <v>0.792643094580515</v>
       </c>
       <c r="K201" s="2" t="n">
         <v>0</v>
@@ -11117,31 +11117,31 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>-0.1272076238951402</v>
+        <v>-0.05493366182545115</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>3115</v>
+        <v>3043</v>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>富榮綱</t>
+          <t>科風</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
         <v/>
       </c>
       <c r="D202" s="2" t="n">
-        <v>184.8365381036545</v>
+        <v>186.3733606055331</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
@@ -11152,13 +11152,13 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>27.17683071258755</v>
+        <v>32.33710617992884</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>6.638014414430016</v>
+        <v>21.36854130071545</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>0.05274782807872908</v>
+        <v>0.8270837206060042</v>
       </c>
       <c r="K202" s="2" t="n">
         <v>0</v>
@@ -11170,31 +11170,31 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>-0.586995142957195</v>
+        <v>-0.1272076239989698</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, mfi_strong</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>2457</v>
+        <v>3115</v>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>飛宏</t>
+          <t>富榮綱</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
         <v/>
       </c>
       <c r="D203" s="2" t="n">
-        <v>171.4823683509885</v>
+        <v>184.8365381036546</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
@@ -11205,13 +11205,13 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>39.62430579876961</v>
+        <v>27.17683073199214</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>19.27084821878662</v>
+        <v>6.638014683532312</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>1.072538322032064</v>
+        <v>0.05274782807872908</v>
       </c>
       <c r="K203" s="2" t="n">
         <v>0</v>
@@ -11223,7 +11223,7 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>-0.06243836364930669</v>
+        <v>-0.5869951429312369</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
@@ -11233,21 +11233,21 @@
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>3028</v>
+        <v>2457</v>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>增你強</t>
+          <t>飛宏</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
         <v/>
       </c>
       <c r="D204" s="2" t="n">
-        <v>170.6710419538983</v>
+        <v>171.4823683509875</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>59.2</v>
+        <v>21</v>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
@@ -11258,49 +11258,49 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>33.6401717381745</v>
+        <v>39.6243058188655</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>16.67189951942093</v>
+        <v>19.27084826549112</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>0.5972830170111316</v>
+        <v>1.072538322032064</v>
       </c>
       <c r="K204" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L204" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M204" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>-0.2631703177555293</v>
+        <v>-0.06243836396079144</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>2701</v>
+        <v>3028</v>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>萬企</t>
+          <t>增你強</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
         <v/>
       </c>
       <c r="D205" s="2" t="n">
-        <v>168.1050654302151</v>
+        <v>170.6710419538983</v>
       </c>
       <c r="E205" s="2" t="n">
-        <v>10.15</v>
+        <v>59.2</v>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
@@ -11311,49 +11311,49 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>35.23202512530672</v>
+        <v>33.64017174771803</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>12.79516017073142</v>
+        <v>16.67189970675269</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>0.9070508501102035</v>
+        <v>0.5972830170111316</v>
       </c>
       <c r="K205" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L205" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M205" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>-0.003783344526163961</v>
+        <v>-0.2631703178204252</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, stronger_than_market</t>
+          <t>avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>2820</v>
+        <v>2701</v>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>華票</t>
+          <t>萬企</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
         <v/>
       </c>
       <c r="D206" s="2" t="n">
-        <v>155.8191762969659</v>
+        <v>168.1050654302151</v>
       </c>
       <c r="E206" s="2" t="n">
-        <v>16.6</v>
+        <v>10.15</v>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
@@ -11364,16 +11364,16 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>42.81558588181791</v>
+        <v>35.23202537230371</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>16.5640713246036</v>
+        <v>12.79516018825631</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>0.6375347548168641</v>
+        <v>0.9070508501102035</v>
       </c>
       <c r="K206" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L206" s="2" t="n">
         <v>0</v>
@@ -11382,7 +11382,7 @@
         <v>-1</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>-0.02750537204438702</v>
+        <v>-0.003783344539141392</v>
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
@@ -11392,21 +11392,21 @@
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>2614</v>
+        <v>2820</v>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>東森</t>
+          <t>華票</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
         <v/>
       </c>
       <c r="D207" s="2" t="n">
-        <v>154.5450137125847</v>
+        <v>155.8191762969659</v>
       </c>
       <c r="E207" s="2" t="n">
-        <v>14.65</v>
+        <v>16.6</v>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
@@ -11417,16 +11417,16 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>18.96720617926162</v>
+        <v>42.81558605469316</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>37.39077839519371</v>
+        <v>16.56407140785111</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>1.092384673918033</v>
+        <v>0.6375347548168641</v>
       </c>
       <c r="K207" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L207" s="2" t="n">
         <v>0</v>
@@ -11435,31 +11435,31 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>-0.1601367446102029</v>
+        <v>-0.02750537204438702</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>3011</v>
+        <v>2614</v>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>今皓</t>
+          <t>東森</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
         <v/>
       </c>
       <c r="D208" s="2" t="n">
-        <v>151.7847591998061</v>
+        <v>154.5450137125839</v>
       </c>
       <c r="E208" s="2" t="n">
-        <v>9.68</v>
+        <v>14.65</v>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
@@ -11470,13 +11470,13 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>41.29094845741099</v>
+        <v>18.96720576132269</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>25.26412810801713</v>
+        <v>37.39077864790909</v>
       </c>
       <c r="J208" s="2" t="n">
-        <v>0.8459612942539827</v>
+        <v>1.092384673918033</v>
       </c>
       <c r="K208" s="2" t="n">
         <v>0</v>
@@ -11488,7 +11488,7 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>0.01984843324019321</v>
+        <v>-0.1601367443506303</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
@@ -11498,21 +11498,21 @@
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>3093</v>
+        <v>3011</v>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>港建*</t>
+          <t>今皓</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
         <v/>
       </c>
       <c r="D209" s="2" t="n">
-        <v>144.287982744288</v>
+        <v>151.7847591998062</v>
       </c>
       <c r="E209" s="2" t="n">
-        <v>37.4</v>
+        <v>9.68</v>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
@@ -11523,16 +11523,16 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>26.32164095511875</v>
+        <v>41.29094830590429</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>32.6609250011344</v>
+        <v>25.26412816901833</v>
       </c>
       <c r="J209" s="2" t="n">
-        <v>0.745224560901022</v>
+        <v>0.8459612942539827</v>
       </c>
       <c r="K209" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L209" s="2" t="n">
         <v>0</v>
@@ -11541,7 +11541,7 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>-0.5646813089262888</v>
+        <v>0.01984843322721414</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
@@ -11551,21 +11551,21 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>2836</v>
+        <v>3093</v>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>高雄銀</t>
+          <t>港建*</t>
         </is>
       </c>
       <c r="C210" s="2" t="n">
         <v/>
       </c>
       <c r="D210" s="2" t="n">
-        <v>135.6900848151696</v>
+        <v>144.2879827442854</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>12</v>
+        <v>37.4</v>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
@@ -11576,16 +11576,16 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>44.884769331556</v>
+        <v>26.32164098062599</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>9.082671386697371</v>
+        <v>32.66092500978933</v>
       </c>
       <c r="J210" s="2" t="n">
-        <v>0.8260426133082037</v>
+        <v>0.745224560901022</v>
       </c>
       <c r="K210" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L210" s="2" t="n">
         <v>0</v>
@@ -11594,31 +11594,31 @@
         <v>-1</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>-0.006523559738418068</v>
+        <v>-0.5646813091339467</v>
       </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, stronger_than_market</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>3050</v>
+        <v>2836</v>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>鈺德</t>
+          <t>高雄銀</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
         <v/>
       </c>
       <c r="D211" s="2" t="n">
-        <v>133.2013100073515</v>
+        <v>135.6900848151696</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>11.4</v>
+        <v>12</v>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
@@ -11629,13 +11629,13 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>46.18787303659515</v>
+        <v>44.88476928444177</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>14.29837702375007</v>
+        <v>9.082671424787145</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>0.864253147715654</v>
+        <v>0.8260426133082037</v>
       </c>
       <c r="K211" s="2" t="n">
         <v>0</v>
@@ -11647,7 +11647,7 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>-0.02419946691718964</v>
+        <v>-0.006523559738418068</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -11657,21 +11657,21 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>2539</v>
+        <v>3050</v>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>櫻花建</t>
+          <t>鈺德</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
         <v/>
       </c>
       <c r="D212" s="2" t="n">
-        <v>122.4441062725388</v>
+        <v>133.2013100073522</v>
       </c>
       <c r="E212" s="2" t="n">
-        <v>32.5</v>
+        <v>11.4</v>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
@@ -11682,13 +11682,13 @@
         <v>0</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>33.2838386822648</v>
+        <v>46.18787323076813</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>19.4332046814907</v>
+        <v>14.29837710249628</v>
       </c>
       <c r="J212" s="2" t="n">
-        <v>2.135439370534526</v>
+        <v>0.864253147715654</v>
       </c>
       <c r="K212" s="2" t="n">
         <v>0</v>
@@ -11700,31 +11700,31 @@
         <v>-1</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>0.02310610638198374</v>
+        <v>-0.02419946702101878</v>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
-          <t>volume_break, avoid_chase</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>愛山林</t>
+          <t>櫻花建</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
         <v/>
       </c>
       <c r="D213" s="2" t="n">
-        <v>120.647577755692</v>
+        <v>122.4441062725389</v>
       </c>
       <c r="E213" s="2" t="n">
-        <v>45.5</v>
+        <v>32.5</v>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
@@ -11735,16 +11735,16 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>35.152295276225</v>
+        <v>33.28383884309672</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>15.41082146747892</v>
+        <v>19.43320486271731</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>1.069602134262409</v>
+        <v>2.135439370534526</v>
       </c>
       <c r="K213" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L213" s="2" t="n">
         <v>0</v>
@@ -11753,31 +11753,31 @@
         <v>-1</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>-0.3518631860199557</v>
+        <v>0.02310610613538633</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase</t>
+          <t>volume_break, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>3056</v>
+        <v>2540</v>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>富華新</t>
+          <t>愛山林</t>
         </is>
       </c>
       <c r="C214" s="2" t="n">
         <v/>
       </c>
       <c r="D214" s="2" t="n">
-        <v>115.2125773874063</v>
+        <v>120.647577755692</v>
       </c>
       <c r="E214" s="2" t="n">
-        <v>13.1</v>
+        <v>45.5</v>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
@@ -11788,16 +11788,16 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>31.46003641430137</v>
+        <v>35.15229542526544</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>17.36164522513823</v>
+        <v>15.41082166557939</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>1.183900032201891</v>
+        <v>1.069602134262409</v>
       </c>
       <c r="K214" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L214" s="2" t="n">
         <v>0</v>
@@ -11806,7 +11806,7 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>-0.05649243759074185</v>
+        <v>-0.3518631865391063</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
@@ -11816,21 +11816,21 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>2497</v>
+        <v>3056</v>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>怡利電</t>
+          <t>富華新</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
         <v/>
       </c>
       <c r="D215" s="2" t="n">
-        <v>113.5413318792636</v>
+        <v>115.2125773873973</v>
       </c>
       <c r="E215" s="2" t="n">
-        <v>42.2</v>
+        <v>13.1</v>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
@@ -11841,13 +11841,13 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>35.96447015108036</v>
+        <v>31.46003673339682</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>13.934487905025</v>
+        <v>17.36164502281333</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>0.7470577939426497</v>
+        <v>1.183900032201891</v>
       </c>
       <c r="K215" s="2" t="n">
         <v>0</v>
@@ -11859,7 +11859,7 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>-0.08797405702153771</v>
+        <v>-0.05649243772052989</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
@@ -11869,21 +11869,21 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>2543</v>
+        <v>2497</v>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>皇昌</t>
+          <t>怡利電</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
         <v/>
       </c>
       <c r="D216" s="2" t="n">
-        <v>111.4539935035314</v>
+        <v>113.5413318792635</v>
       </c>
       <c r="E216" s="2" t="n">
-        <v>37.1</v>
+        <v>42.2</v>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
@@ -11894,16 +11894,16 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>38.31474407308174</v>
+        <v>35.9644703017505</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>19.80724512800383</v>
+        <v>13.93448790399938</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>1.140735053551617</v>
+        <v>0.7470577939426497</v>
       </c>
       <c r="K216" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L216" s="2" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>-0.160050682403189</v>
+        <v>-0.08797405754068605</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -11922,21 +11922,21 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>根基</t>
+          <t>皇昌</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
         <v/>
       </c>
       <c r="D217" s="2" t="n">
-        <v>105.8572673239984</v>
+        <v>111.4539935035338</v>
       </c>
       <c r="E217" s="2" t="n">
-        <v>102.5</v>
+        <v>37.1</v>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
@@ -11947,16 +11947,16 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>42.38747914582493</v>
+        <v>38.31474272550329</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>15.66224264726653</v>
+        <v>19.8072450481784</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>0.6255690494344768</v>
+        <v>1.140735053551617</v>
       </c>
       <c r="K217" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L217" s="2" t="n">
         <v>0</v>
@@ -11965,31 +11965,31 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>-0.4768592882404496</v>
+        <v>-0.1600506821955281</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>2534</v>
+        <v>2546</v>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>宏盛</t>
+          <t>根基</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
         <v/>
       </c>
       <c r="D218" s="2" t="n">
-        <v>105.113375372524</v>
+        <v>105.8572673239984</v>
       </c>
       <c r="E218" s="2" t="n">
-        <v>16.05</v>
+        <v>102.5</v>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
@@ -12000,13 +12000,13 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>29.15798017229643</v>
+        <v>42.38747917495705</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>17.40966634783352</v>
+        <v>15.66224258807412</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>1.150704985032148</v>
+        <v>0.6255690494344768</v>
       </c>
       <c r="K218" s="2" t="n">
         <v>0</v>
@@ -12018,31 +12018,31 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>-0.04504399110521273</v>
+        <v>-0.4768592881885362</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase</t>
+          <t>ema60_gt_ema120, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>2462</v>
+        <v>2534</v>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>良得電</t>
+          <t>宏盛</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
         <v/>
       </c>
       <c r="D219" s="2" t="n">
-        <v>66.75369853960177</v>
+        <v>105.113375372524</v>
       </c>
       <c r="E219" s="2" t="n">
-        <v>18.7</v>
+        <v>16.05</v>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
@@ -12053,13 +12053,13 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>38.12981929041268</v>
+        <v>29.15798030195127</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>15.61728080873861</v>
+        <v>17.40966640224034</v>
       </c>
       <c r="J219" s="2" t="n">
-        <v>1.175243358263186</v>
+        <v>1.150704985032148</v>
       </c>
       <c r="K219" s="2" t="n">
         <v>0</v>
@@ -12071,7 +12071,7 @@
         <v>-1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>-0.09810294758270002</v>
+        <v>-0.04504399110521273</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
@@ -12081,21 +12081,21 @@
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>3018</v>
+        <v>2462</v>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>隆銘綠能</t>
+          <t>良得電</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
         <v/>
       </c>
       <c r="D220" s="2" t="n">
-        <v>59.49543919789046</v>
+        <v>66.75369853960517</v>
       </c>
       <c r="E220" s="2" t="n">
-        <v>10.2</v>
+        <v>18.7</v>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
@@ -12106,13 +12106,13 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>49.03105047441107</v>
+        <v>38.12981930813263</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>23.20550707342393</v>
+        <v>15.61728087996966</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>0.4789460092041708</v>
+        <v>1.175243358263186</v>
       </c>
       <c r="K220" s="2" t="n">
         <v>0</v>
@@ -12124,31 +12124,31 @@
         <v>-1</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>-0.2523954888273324</v>
+        <v>-0.09810294767354874</v>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, adx_trending</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>2949</v>
+        <v>3018</v>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>欣新網</t>
+          <t>隆銘綠能</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
         <v/>
       </c>
       <c r="D221" s="2" t="n">
-        <v>44.97485238389897</v>
+        <v>59.49543919789046</v>
       </c>
       <c r="E221" s="2" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
@@ -12159,13 +12159,13 @@
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>46.32490311929367</v>
+        <v>49.03105048059314</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>7.762997928314968</v>
+        <v>23.20550705563988</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>0.02263961093409358</v>
+        <v>0.4789460092041708</v>
       </c>
       <c r="K221" s="2" t="n">
         <v>0</v>
@@ -12177,60 +12177,113 @@
         <v>-1</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>0.4088147425086031</v>
-      </c>
-      <c r="O221" s="2" t="n">
-        <v/>
+        <v>-0.2523954888662685</v>
+      </c>
+      <c r="O221" s="2" t="inlineStr">
+        <is>
+          <t>avoid_chase, adx_trending</t>
+        </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
+        <v>2949</v>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>欣新網</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D222" s="2" t="n">
+        <v>44.97485238389897</v>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H222" s="2" t="n">
+        <v>46.32490309461532</v>
+      </c>
+      <c r="I222" s="2" t="n">
+        <v>7.762997886991726</v>
+      </c>
+      <c r="J222" s="2" t="n">
+        <v>0.02263961093409358</v>
+      </c>
+      <c r="K222" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N222" s="2" t="n">
+        <v>0.4088147424047737</v>
+      </c>
+      <c r="O222" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
         <v>3015</v>
       </c>
-      <c r="B222" s="2" t="inlineStr">
+      <c r="B223" s="2" t="inlineStr">
         <is>
           <t>全漢</t>
         </is>
       </c>
-      <c r="C222" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D222" s="2" t="n">
+      <c r="C223" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D223" s="2" t="n">
         <v>40.98456461468169</v>
       </c>
-      <c r="E222" s="2" t="n">
+      <c r="E223" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="F222" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G222" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H222" s="2" t="n">
-        <v>36.03484560790106</v>
-      </c>
-      <c r="I222" s="2" t="n">
-        <v>19.10102546115262</v>
-      </c>
-      <c r="J222" s="2" t="n">
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H223" s="2" t="n">
+        <v>36.03484575680191</v>
+      </c>
+      <c r="I223" s="2" t="n">
+        <v>19.10102546667142</v>
+      </c>
+      <c r="J223" s="2" t="n">
         <v>0.7159176433644101</v>
       </c>
-      <c r="K222" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L222" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M222" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N222" s="2" t="n">
-        <v>-0.2536388622503533</v>
-      </c>
-      <c r="O222" s="2" t="inlineStr">
+      <c r="K223" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N223" s="2" t="n">
+        <v>-0.2536388627694975</v>
+      </c>
+      <c r="O223" s="2" t="inlineStr">
         <is>
           <t>avoid_chase</t>
         </is>

--- a/output/full_scan/batch_seq3_2026-10-22.xlsx
+++ b/output/full_scan/batch_seq3_2026-10-22.xlsx
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>59.80106338864974</v>
+        <v>59.80106345083263</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>14.23539171888559</v>
+        <v>14.2353916641176</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>5.604635508237373</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3944770132433513</v>
+        <v>0.394477012682652</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>59.57431076949047</v>
+        <v>59.57431089733468</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>21.01834392022064</v>
+        <v>21.01834407537214</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.5050085910566</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.05734852012305858</v>
+        <v>-0.05734852082390196</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1172.239747635106</v>
+        <v>1172.239747635107</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>125.5</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>70.38758018822661</v>
+        <v>70.38758050987239</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>32.04339983812174</v>
+        <v>32.0433998987894</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>1.678069002562811</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.6103091796789775</v>
+        <v>0.6103091800994747</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>60.56630408944484</v>
+        <v>60.5663040617344</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>25.10586990843579</v>
+        <v>25.10586978356455</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1.195403088141908</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.01952106077584859</v>
+        <v>-0.01952106066371595</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>55.67333607508785</v>
+        <v>55.67333610125998</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>29.57014577946339</v>
+        <v>29.57014600852432</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0.8223457768484115</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1599015880031063</v>
+        <v>-0.1599015882273784</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>66.8772007103008</v>
+        <v>66.87720068586505</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>37.41848755986882</v>
+        <v>37.41848752207122</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1.346346242874108</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1701029440742234</v>
+        <v>0.1701029442424291</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>967.2689811444857</v>
+        <v>967.2689811444858</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>245.5</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>69.72865349618573</v>
+        <v>69.72865358983604</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>36.34536836779114</v>
+        <v>36.34536841865981</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>0.7157272660294796</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.8665002604045191</v>
+        <v>0.8665002605447105</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>59.95831240995898</v>
+        <v>59.95831246388612</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>26.91253666583384</v>
+        <v>26.91253676329498</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>0.7455094456534527</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.02920704796029795</v>
+        <v>0.02920704794628334</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>72.97433627816002</v>
+        <v>72.97433630264185</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>42.98956776231916</v>
+        <v>42.98956799502324</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>2.945998223547903</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.600960404791957</v>
+        <v>0.6009604043153742</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>61.55664834391103</v>
+        <v>61.55664836481338</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>28.2530427122574</v>
+        <v>28.25304297101706</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>0.6907989432775367</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.9562086139880579</v>
+        <v>0.9562086137077284</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>76.22529626477993</v>
+        <v>76.22529620527531</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>42.13003386972692</v>
+        <v>42.1300339471357</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>1.12505222899752</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.6465127787129417</v>
+        <v>0.64651277885311</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>69.8371736026926</v>
+        <v>69.83717356120658</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>44.73862637463653</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.07537932150849258</v>
+        <v>0.07537932153652338</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>77.97248146523248</v>
+        <v>77.97248146902015</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>63.95874263706654</v>
+        <v>63.95874264041888</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>2.342619311936744</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>6.235141421401252</v>
+        <v>6.2351414212891</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>57.95758493928318</v>
+        <v>57.95758501222701</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>30.19177216770548</v>
+        <v>30.19177234399339</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>1.852443641606935</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.4142874182602796</v>
+        <v>0.4142874178958267</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>67.19417189418813</v>
+        <v>67.19417185775825</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>25.02700816648467</v>
+        <v>25.02700812027296</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>1.012030917740277</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.4693127944437998</v>
+        <v>0.4693127946120108</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>71.36493483598061</v>
+        <v>71.36493480544361</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>43.79753157404687</v>
+        <v>43.79753156046586</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1.075990154397204</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.1662829158773194</v>
+        <v>0.1662829159754355</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>72.57483591813846</v>
+        <v>72.57483590108383</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>34.70793810919041</v>
+        <v>34.70793816601118</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>1.012925788046394</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.4739233420312057</v>
+        <v>0.473923342115306</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>71.81952205893865</v>
+        <v>71.81952205485747</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>40.8643692108154</v>
+        <v>40.86436922905408</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>1.042553710793667</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.1196680481895162</v>
+        <v>0.1196680482595961</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>67.41933173821209</v>
+        <v>67.41933184842682</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>51.72762983052566</v>
+        <v>51.72763003475465</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>0.5617301792409402</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.9178057492961589</v>
+        <v>0.9178057485953346</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>832.7011989217673</v>
+        <v>832.7011989217672</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>583</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>61.6008127995416</v>
+        <v>61.60081278230909</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>25.11068070356847</v>
+        <v>25.11068079301592</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.7364609538964125</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>4.391973179580498</v>
+        <v>4.391973180701859</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>816.5579697323935</v>
+        <v>816.5579697323936</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>15.55</v>
@@ -1612,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>61.09070851136455</v>
+        <v>61.090708571998</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>43.50401940642036</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.008889902627768287</v>
+        <v>-0.008889902655802639</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>813.5424470797773</v>
+        <v>813.542447079777</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>32.2</v>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>62.60627147029199</v>
+        <v>62.60627151426846</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>18.50681536615268</v>
+        <v>18.50681541274151</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>1.277648133410794</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.09613518994310263</v>
+        <v>0.09613518990105313</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>57.60691593959687</v>
+        <v>57.60691598858811</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>36.5404469071664</v>
+        <v>36.54044712214989</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>0.7889967476135447</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.2528476756338192</v>
+        <v>-0.2528476757739877</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>56.27227254296977</v>
+        <v>56.2722725322072</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>15.77993526242127</v>
+        <v>15.77993528584628</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>0.9023181740181346</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.4781863716775545</v>
+        <v>-0.4781863715373693</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>53.2149222848541</v>
+        <v>53.21492225138925</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>28.96358975411489</v>
+        <v>28.9635899550509</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>0.6877168930930208</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.225749936782583</v>
+        <v>-0.2257499369507934</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>64.55989995637165</v>
+        <v>64.55989996998721</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>44.8744714858167</v>
+        <v>44.87447150035209</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>1.604622719870239</v>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>64.91842471822744</v>
+        <v>64.91842447324063</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>21.277252736604</v>
+        <v>21.27725278048938</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>1.337822769850339</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.07871718814383158</v>
+        <v>0.07871718824195126</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>59.68173919797805</v>
+        <v>59.68173443253854</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>39.04824946982505</v>
+        <v>39.04825362464783</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>3.448151378147454</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.03402947072829066</v>
+        <v>-0.03402946988437552</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>56.34456258921541</v>
+        <v>56.34456266911697</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>34.33020246666523</v>
+        <v>34.33020238831327</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.4659466481919292</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.01346586626278645</v>
+        <v>-0.01346586616466799</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>717.4339295706784</v>
+        <v>717.4339295706774</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>22.35</v>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>52.0659108694322</v>
+        <v>52.06591098668599</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>32.80356099549325</v>
+        <v>32.80356109602146</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>0.6582301498904217</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.01906348111294354</v>
+        <v>-0.01906348121106433</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>67.90867568939041</v>
+        <v>67.90867572461985</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>36.74719989276585</v>
+        <v>36.74719997521086</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.7588037569183914</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.09395232939881959</v>
+        <v>0.09395232938480336</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>708.4750097931701</v>
+        <v>708.47500979317</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>226</v>
@@ -2198,7 +2198,7 @@
         <v>65.37271236483534</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>32.46640172285811</v>
+        <v>32.4664018107806</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0.7860595746945929</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>1.581722322248676</v>
+        <v>1.581722322388815</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>54.01002527128808</v>
+        <v>54.01002523702897</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>27.02462030355594</v>
+        <v>27.02462019174483</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.8675822415334251</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.2071288464208894</v>
+        <v>-0.2071288461685892</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>40.85927606532302</v>
+        <v>40.85927605714421</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>22.2875662849391</v>
+        <v>22.28756618209042</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.7501028772475842</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.33722391587486</v>
+        <v>0.3372239158888735</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>50.46315436957536</v>
+        <v>50.46315431896377</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>24.37396637774441</v>
+        <v>24.37396642212846</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>0.8412893145049817</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.2557313966819436</v>
+        <v>-0.2557313966258765</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>673.1863457397013</v>
+        <v>673.1863457397025</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>158.5</v>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>58.56479690306092</v>
+        <v>58.56479681150982</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>29.74885907595943</v>
+        <v>29.74885897472856</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>0.6465001609567638</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.3772688425138533</v>
+        <v>-0.3772688418690966</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>54.40012780037176</v>
+        <v>54.40012780741612</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>8.061457714129059</v>
+        <v>8.061457725151763</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>9.747582263852564</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.147771500556278</v>
+        <v>0.1477715003740564</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>648.9014142314064</v>
+        <v>648.9014142314063</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>141</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>49.11574183775809</v>
+        <v>49.11574197208022</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>32.53853449291717</v>
+        <v>32.53853465715252</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.3166670520886173</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.8632749651006923</v>
+        <v>-0.8632749653810294</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>58.61145736496871</v>
+        <v>58.61145735138858</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>38.84382277092594</v>
+        <v>38.8438226899794</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.4595582803252993</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.03912638850702632</v>
+        <v>0.03912638857710915</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>53.78377298671629</v>
+        <v>53.78377299622972</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>19.76486825815594</v>
+        <v>19.76486810828564</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.370066424675075</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.001933579425331282</v>
+        <v>-0.001933579422527601</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.27980686321779</v>
+        <v>51.27980686359981</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>27.80058416202355</v>
+        <v>27.80058422844307</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>1.6584113968261</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-3.240398617182777</v>
+        <v>-3.24039861735098</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>41.50469369934297</v>
+        <v>41.50469374104365</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>37.79536723289028</v>
+        <v>37.79536737536723</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.2859672388961456</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-2.31604927243496</v>
+        <v>-2.316049272617182</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>57.29012261833646</v>
+        <v>57.29012279215706</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>47.71210525077854</v>
+        <v>47.71210532465266</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.1010206906414065</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.02012105905109079</v>
+        <v>-0.02012105910715833</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>51.79704035366276</v>
+        <v>51.79704105042803</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>13.57134028446269</v>
+        <v>13.57134110903701</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.900219540004771</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.03376423166897904</v>
+        <v>0.03376423138863877</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>592.999193333157</v>
+        <v>592.9991933331657</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>14.55</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>52.27073651931214</v>
+        <v>52.27073761532935</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>21.58634612234723</v>
+        <v>21.5863461542692</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.9724630380057481</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.002208630527979677</v>
+        <v>0.002208630121485811</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>590.9638550309338</v>
+        <v>590.9638550309346</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>170</v>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>59.11154153666048</v>
+        <v>59.1115415158536</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>11.94416911514913</v>
+        <v>11.94416905395778</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>1.244584445629161</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.5847032188925095</v>
+        <v>0.5847032190326784</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>53.23795175434103</v>
+        <v>53.23795188723082</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>23.10468692030992</v>
+        <v>23.10468692079254</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.4448238616571399</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.01978194795213106</v>
+        <v>-0.01978194767176245</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>55.05952863057924</v>
+        <v>55.05952861066626</v>
       </c>
       <c r="I49" s="2" t="n">
         <v>51.88711367675793</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.00651349703760129</v>
+        <v>-0.006513496995549151</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>574.551808564299</v>
+        <v>574.5518085642991</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>20.5</v>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>51.1474334275975</v>
+        <v>51.14743325504384</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>17.17305453666027</v>
+        <v>17.17305470108379</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.7993140433268333</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.02130324992924805</v>
+        <v>0.02130325004138419</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>556.9997250789424</v>
+        <v>556.9997250789427</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>1085</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>45.83365822200719</v>
+        <v>45.8336582313595</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>18.9502907906515</v>
+        <v>18.95029097593707</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>1.343156454907459</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-24.4457506363</v>
+        <v>-24.44575063728124</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>57.50850895102734</v>
+        <v>57.50850890748746</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>44.25731262521241</v>
+        <v>44.25731262905784</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.87146289226673</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.02672480584560599</v>
+        <v>0.02672480588765763</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>53.63898612800837</v>
+        <v>53.638986185287</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>29.21562606844949</v>
+        <v>29.21562624586361</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.4380875863965594</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.07402694764631579</v>
+        <v>-0.07402694773041407</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>46.83110001653554</v>
+        <v>46.83110011262274</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>27.228118743154</v>
+        <v>27.22811876423991</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.2724889263666855</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.3751208465902734</v>
+        <v>-0.3751208467024102</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>54.59254701224169</v>
+        <v>54.59254701460205</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>37.19820826043623</v>
+        <v>37.19820828309661</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>0.469779550763363</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.05130334330272124</v>
+        <v>0.05130334328870489</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>46.33936668913353</v>
+        <v>46.33936673202653</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>35.99538136743533</v>
+        <v>35.99538135540838</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>0.3107656274756301</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-5.440734089246096</v>
+        <v>-5.440734089274121</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>52.21280626217998</v>
+        <v>52.21280628235073</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>13.8207160346565</v>
+        <v>13.82071610513805</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>1.975161497612949</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.02133352082983971</v>
+        <v>-0.02133352088590441</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>54.95694222161737</v>
+        <v>54.95694217946155</v>
       </c>
       <c r="I58" s="2" t="n">
         <v>24.64764204161234</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.009053041239088233</v>
+        <v>0.009053041267125153</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>46.79175362430315</v>
+        <v>46.79175364951806</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>13.29896717062897</v>
+        <v>13.29896736248939</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>1.665316563296289</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.216569149915438</v>
+        <v>-0.2165691500266562</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>48.92002952796356</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>6.171766270509021</v>
+        <v>6.171766270509022</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>1.556703646938216</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>53.07665971654347</v>
+        <v>53.07665974726068</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>42.70906458386892</v>
+        <v>42.70906460926137</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.7610589791480448</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.2267510110463978</v>
+        <v>-0.2267510110744332</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>52.37979936993211</v>
+        <v>52.37979937496168</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>17.89227277898258</v>
+        <v>17.8922727383044</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>0.9409445925915478</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.1645175485343277</v>
+        <v>-0.164517548464251</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>41.05162903541824</v>
+        <v>41.05162900771633</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>7.093919683293741</v>
+        <v>7.093919697449084</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.9936198555364365</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.03214089849494517</v>
+        <v>0.03214090073764453</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>47.48104039272584</v>
+        <v>47.48104038234221</v>
       </c>
       <c r="I64" s="2" t="n">
         <v>32.89498636856455</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.744023004970185</v>
+        <v>-0.7440230049281329</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>53.56875359848696</v>
+        <v>53.56875365946945</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>35.67246141932844</v>
+        <v>35.67246153942605</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.9352769891595933</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.1714396517412755</v>
+        <v>-0.1714396518747323</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>506.8235029599057</v>
+        <v>506.8235029599039</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>11.25</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>53.89454114211946</v>
+        <v>53.89454125130028</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>35.01620626703629</v>
+        <v>35.01620628556267</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.4909582591832417</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.02591744858417453</v>
+        <v>0.02591744855613915</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>46.83028306484713</v>
+        <v>46.83028325000889</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>22.65372910514331</v>
+        <v>22.65372912685234</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>1.105926777129552</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.02064688747386842</v>
+        <v>0.02064688748788635</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>500.6513091358423</v>
+        <v>500.6513091358427</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>144</v>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>51.36212090435313</v>
+        <v>51.36212112877428</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10.34999990475773</v>
+        <v>10.34999998952277</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>0.9329043384208081</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.02071519400603854</v>
+        <v>-0.02071519372570053</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>53.08371503291552</v>
+        <v>53.08371503870372</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>37.12994939153366</v>
+        <v>37.12994947333382</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>0.3680487664615562</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1342945216939937</v>
+        <v>-0.1342945217640792</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>47.65306062265842</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>10.31993087098116</v>
+        <v>10.31993086286074</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.8048861985460785</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.1535643723124661</v>
+        <v>-0.1535643723685309</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>49.07252872741659</v>
+        <v>49.07252875628929</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>4.699080741282998</v>
+        <v>4.699081126778703</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>2.520646498963303</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.04051167085926509</v>
+        <v>0.04051167035465123</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>51.9134041682323</v>
+        <v>51.91340422110769</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>29.16926024517759</v>
+        <v>29.16926030979461</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>1.206872808767379</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-3.542475732899128</v>
+        <v>-3.542475735001624</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>44.54392530633835</v>
+        <v>44.54392531312157</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>19.79512375067669</v>
+        <v>19.79512384895372</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.5253873156560308</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.2077556598313061</v>
+        <v>-0.2077556599013915</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>43.17182357422524</v>
+        <v>43.17182355925723</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>12.69403486399327</v>
+        <v>12.69403487516029</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.800702741839606</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-41.23375759257596</v>
+        <v>-41.23375759033362</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>485.1608812619963</v>
+        <v>485.1608812619897</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>18</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>43.87524360766981</v>
+        <v>43.87524365957815</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>31.13029377551366</v>
+        <v>31.13029379290228</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.5614772909929824</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.1624460694535121</v>
+        <v>-0.162446069551633</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>42.77477790833077</v>
+        <v>42.77477783634116</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>22.97709434011112</v>
+        <v>22.97709441660161</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.6367793481253671</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.5336835380700472</v>
+        <v>-0.5336835379859515</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>46.6894886384186</v>
+        <v>46.68948864079885</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>25.99309183061177</v>
+        <v>25.99309190198116</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>1.040022166993571</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-10.94021187448947</v>
+        <v>-10.94021187462967</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>478.4223458335378</v>
+        <v>478.4223458335384</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>121.5</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>51.78696267233168</v>
+        <v>51.7869622216967</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>22.86635621813099</v>
+        <v>22.86635625379521</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.6072533339872901</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.3421922629375248</v>
+        <v>0.3421922665819367</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>46.8410354703251</v>
+        <v>46.84103550025517</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>11.95972621701783</v>
+        <v>11.95972624617033</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>0.8859614575116446</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.1032389038437878</v>
+        <v>-0.1032389038998527</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>48.70681820029864</v>
+        <v>48.70681809112166</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>8.683878231249357</v>
+        <v>8.68387819127614</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>0.4978967031178403</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>45.27691188389444</v>
+        <v>45.27691189137048</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>24.42820179900988</v>
+        <v>24.42820183127479</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>1.013953057957626</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-13.44172837753777</v>
+        <v>-13.44172837790227</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>53.81149372592903</v>
+        <v>53.81149374410006</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>21.26580545517053</v>
+        <v>21.26580563921226</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>2.44493620307061</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.07221827432693295</v>
+        <v>-0.07221827439701922</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>39.27163587314165</v>
+        <v>39.27163589179499</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>25.8437223703811</v>
+        <v>25.84372247718824</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.6573905201305341</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-12.86534648587221</v>
+        <v>-12.86534648699352</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>45.20809505364588</v>
+        <v>45.20809505768486</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>28.00637378519643</v>
+        <v>28.00637387969033</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.495486720427454</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-1.101479534108838</v>
+        <v>-1.101479534080805</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>448.8227787120892</v>
+        <v>448.8227787120886</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>18.55</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>48.12741572943356</v>
+        <v>48.12741586281079</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>23.87526020994164</v>
+        <v>23.87526025352035</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.4752929231042735</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.03730053305323908</v>
+        <v>-0.03730053322143978</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>38.94192766538842</v>
+        <v>38.94193099538997</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>22.50332397506807</v>
+        <v>22.50332392229193</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.5278350593087376</v>
@@ -5043,7 +5043,7 @@
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>445.623067970821</v>
+        <v>445.6230679708192</v>
       </c>
       <c r="E87" s="2" t="n">
         <v>38.3</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>48.37121670485817</v>
+        <v>48.37121729750321</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>13.53951277386313</v>
+        <v>13.53951292426434</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>0.8245432064596556</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.04616740250353066</v>
+        <v>0.04616740236335967</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>444.6397526349255</v>
+        <v>444.6397526349253</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>79.40000000000001</v>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>51.38553168735976</v>
+        <v>51.38553199276977</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12.52878689794829</v>
+        <v>12.52878698918115</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>1.712522405083917</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.2478866324342601</v>
+        <v>0.2478866320698152</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>47.47114522904082</v>
+        <v>47.47114520141055</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>20.20175714427729</v>
+        <v>20.2017572047246</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.8767545255598808</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.322909477773369</v>
+        <v>-0.3229094778854955</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>41.17553352191479</v>
+        <v>41.17553362528365</v>
       </c>
       <c r="I90" s="2" t="n">
         <v>26.51123823387077</v>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>42.64083891130211</v>
+        <v>42.64083889402381</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>22.24614772171642</v>
+        <v>22.2461476651872</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>0.730259044475385</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-2.787742601438355</v>
+        <v>-2.787742600232895</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>43.73970544791885</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>27.35387349526748</v>
+        <v>27.3538735646368</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.5688715334330581</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.3638841275339031</v>
+        <v>-0.3638841275899698</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>49.40485580410974</v>
+        <v>49.40485577090087</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>28.44968757341286</v>
+        <v>28.44968757900783</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.8371232499983399</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.5023187368247415</v>
+        <v>-0.5023187367406425</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>436.590746457929</v>
+        <v>436.5907464579291</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>22.05</v>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>52.08657065436058</v>
+        <v>52.08657054435563</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>18.59101773768113</v>
+        <v>18.59101805221772</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.9528190605725229</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.01588496616626089</v>
+        <v>-0.01588496611019321</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>436.4266321632602</v>
+        <v>436.4266321632626</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>114</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>32.36137707409225</v>
+        <v>32.36137718932994</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>16.00203831060637</v>
+        <v>16.0020383663867</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>1.873961677944835</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-1.332479178346898</v>
+        <v>-1.332479178627235</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>45.67077965126089</v>
+        <v>45.67077961788947</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>23.03758103609027</v>
+        <v>23.03758114947521</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.5488713602307305</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0261182120827266</v>
+        <v>-0.02611821209674394</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>44.42015875163243</v>
+        <v>44.42015880131184</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>18.26833914559043</v>
+        <v>18.26833925131026</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>0.6509163934228407</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1473318738282373</v>
+        <v>-0.1473318739123374</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>41.91043120488222</v>
+        <v>41.91043126288929</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>21.77370867469745</v>
+        <v>21.77370895192095</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>1.071238337311583</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-5.052638557597456</v>
+        <v>-5.052638559419667</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>40.41598142204839</v>
+        <v>40.41598183221154</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>14.3229895718893</v>
+        <v>14.3229896605451</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.6470130511401305</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1859809144800392</v>
+        <v>-0.1859809140875601</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>42.07377420652987</v>
+        <v>42.07377384795236</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>26.14643316198458</v>
+        <v>26.1464332725426</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>1.060399340896713</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.03868517845935211</v>
+        <v>-0.0386851783752525</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>49.95121067066705</v>
+        <v>49.95121112615242</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>15.42952483037219</v>
+        <v>15.42952484962172</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.8483701382935951</v>
@@ -5852,7 +5852,7 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>45.81511446468344</v>
+        <v>45.81511426932442</v>
       </c>
       <c r="I102" s="2" t="n">
         <v>17.80709823300852</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.1896641008760265</v>
+        <v>-0.189664100623716</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>403.5023337069973</v>
+        <v>403.5023337069974</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>263</v>
@@ -5905,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>34.88685929106849</v>
+        <v>34.88685927603373</v>
       </c>
       <c r="I103" s="2" t="n">
         <v>20.66932945865431</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-3.870409543508266</v>
+        <v>-3.870409543227977</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>49.10953948404911</v>
+        <v>49.10953957453375</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>27.07647882051887</v>
+        <v>27.07647884663891</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.6988683902914974</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.02529868885393266</v>
+        <v>-0.02529868898008902</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>33.85773190159377</v>
+        <v>33.85773193065013</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>22.67298570290092</v>
+        <v>22.67298553963462</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.8222255124153995</v>
@@ -6050,7 +6050,7 @@
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>390.497098978286</v>
+        <v>390.4970989782861</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>298</v>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>36.98827083033219</v>
+        <v>36.988270806017</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>14.52571195555533</v>
+        <v>14.52571198367911</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>1.307479480645701</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-1.974283070021924</v>
+        <v>-1.974283069881764</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>390.1092336294535</v>
+        <v>390.109233629454</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>91.5</v>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>49.77105735130201</v>
+        <v>49.77105742017839</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>27.41673746286032</v>
+        <v>27.41673753174591</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.7679384861856485</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.1257648218329566</v>
+        <v>-0.1257648225337942</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>46.75640556158162</v>
+        <v>46.75640558972043</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>18.89521193480687</v>
+        <v>18.89521210913684</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.607927533512832</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-2.321480761152322</v>
+        <v>-2.321480761432646</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>37.81689925853425</v>
+        <v>37.81689926346754</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>37.11102370471477</v>
+        <v>37.11102375643321</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.1518974943607057</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-8.876823159094666</v>
+        <v>-8.876823159262869</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>48.65669568902257</v>
+        <v>48.65669563575528</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>15.14932077220113</v>
+        <v>15.1493207401289</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.7185551512186255</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.02234942004885457</v>
+        <v>-0.02234941992270637</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>377.3845010997571</v>
+        <v>377.3845010997535</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>11.7</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>41.87114738784366</v>
+        <v>41.8711472561831</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>20.55425339470697</v>
+        <v>20.55425341146744</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>1.319899338045222</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.01435131430775665</v>
+        <v>-0.01435131427972183</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>376.0715795091467</v>
+        <v>376.0715795091472</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>53.1</v>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>50.59434824800838</v>
+        <v>50.5943483952047</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>18.02081375887622</v>
+        <v>18.02081402382176</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>1.691879909301246</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.06075486939998297</v>
+        <v>-0.06075486962425188</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>42.6620991251279</v>
+        <v>42.66209913909583</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>14.09391322444818</v>
+        <v>14.09391330697479</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0.5308942743097778</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.06231741448990902</v>
+        <v>0.06231741447589312</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>362.296961050352</v>
+        <v>362.2969610503525</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>8.09</v>
@@ -6491,7 +6491,7 @@
         <v>27.37457659809145</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>20.45299496271462</v>
+        <v>20.45299491988119</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.9839021880430603</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.01649831257588159</v>
+        <v>-0.01649831257868495</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>360.4017068205664</v>
+        <v>360.4017068205662</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>234</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>39.53712844647093</v>
+        <v>39.5371284573101</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>19.76388185797643</v>
+        <v>19.76388187290726</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.6324881264386338</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-3.536874083687048</v>
+        <v>-3.53687408371505</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>359.5497638187189</v>
+        <v>359.5497638187184</v>
       </c>
       <c r="E116" s="2" t="n">
         <v>11.95</v>
@@ -6597,7 +6597,7 @@
         <v>35.61637468899596</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>26.79518263809319</v>
+        <v>26.79518257659187</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.9786826390194551</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.01476299439451786</v>
+        <v>-0.01476299442255147</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>51.18469204515686</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>13.04898601508897</v>
+        <v>13.04898604784206</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>0.946101691395583</v>
@@ -6700,7 +6700,7 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>43.62278840272374</v>
+        <v>43.62278841896946</v>
       </c>
       <c r="I118" s="2" t="n">
         <v>23.88707707555657</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.2542850801335612</v>
+        <v>-0.2542850801195407</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>45.53355186422015</v>
+        <v>45.53355186937561</v>
       </c>
       <c r="I119" s="2" t="n">
         <v>14.75517586352564</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.9866903745029569</v>
+        <v>-0.9866903743347066</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>357.1473481669603</v>
+        <v>357.1473481669836</v>
       </c>
       <c r="E120" s="2" t="n">
         <v>23.2</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>46.86021114489331</v>
+        <v>46.86021119281853</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>17.69051572864241</v>
+        <v>17.6905157052574</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>0.4152552316399888</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.004736167786185443</v>
+        <v>-0.004736167856269874</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>355.2117365649196</v>
+        <v>355.2117365649197</v>
       </c>
       <c r="E121" s="2" t="n">
         <v>9.869999999999999</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>49.19516831585831</v>
+        <v>49.19516853235635</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>13.14299964974114</v>
+        <v>13.14299954094678</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.7818919386444556</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.02162618087455014</v>
+        <v>0.02162618086053424</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>354.5976336285177</v>
+        <v>354.5976336285179</v>
       </c>
       <c r="E122" s="2" t="n">
         <v>33.2</v>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>41.9465845092606</v>
+        <v>41.94658431246064</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>8.270901397840115</v>
+        <v>8.270901307807048</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>0.5106968315253584</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.03748475168900461</v>
+        <v>-0.03748475107225313</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>46.54946329495967</v>
+        <v>46.54946319206312</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>17.06379536879247</v>
+        <v>17.06379541379732</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.8636088952282992</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.02097689940962885</v>
+        <v>0.02097689942364647</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>352.384746231875</v>
+        <v>352.3847462318751</v>
       </c>
       <c r="E124" s="2" t="n">
         <v>118.5</v>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>43.94160228087711</v>
+        <v>43.94160229036559</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>14.04352420528384</v>
+        <v>14.04352428702349</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.8847943368095003</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.9966979250726871</v>
+        <v>-0.9966979252268726</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>351.7129569569793</v>
+        <v>351.7129569569794</v>
       </c>
       <c r="E125" s="2" t="n">
         <v>6175</v>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>45.96235812293177</v>
+        <v>45.96235812471156</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>13.78237983254298</v>
+        <v>13.78237983737258</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.6587573071978704</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-99.37802425919395</v>
+        <v>-99.37802425498927</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>31.30022974262661</v>
+        <v>31.30022975316071</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>22.7601620306583</v>
+        <v>22.76016212869622</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>0.7609791259070073</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-3.019720009930274</v>
+        <v>-3.019720009902244</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>43.4109753529357</v>
+        <v>43.41097546759384</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>9.320403984539277</v>
+        <v>9.320403964337084</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.7210475739300293</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.03819265614242087</v>
+        <v>-0.0381926561984865</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>47.46687756665811</v>
+        <v>47.46687759091393</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>13.34938997251889</v>
+        <v>13.34938991537181</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>0.3716251344584184</v>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>31.37275800372409</v>
+        <v>31.37275795791021</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>33.7185971328695</v>
+        <v>33.71859721371535</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>1.147283405493178</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.01177867937297417</v>
+        <v>0.01177867935895507</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>42.15339534976031</v>
+        <v>42.15339501871704</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>20.72654248518852</v>
+        <v>20.72654262008674</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>0.6299392841426403</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.1503423136319096</v>
+        <v>-0.1503423104079986</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>338.7279337865271</v>
+        <v>338.7279337865273</v>
       </c>
       <c r="E131" s="2" t="n">
         <v>89.2</v>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>49.10992091921439</v>
+        <v>49.1099209297759</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>11.00466325597341</v>
+        <v>11.00466316858983</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>0.744336204905148</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.08268817744614115</v>
+        <v>-0.08268817747417401</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>336.898507506295</v>
+        <v>336.8985075062948</v>
       </c>
       <c r="E132" s="2" t="n">
         <v>147.5</v>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>33.95606871733523</v>
+        <v>33.95606869461515</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>19.65033871663909</v>
+        <v>19.65033861379094</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>4.507653730532818</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-0.8662375701098605</v>
+        <v>-0.86623756996968</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>46.26471674936219</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>21.94015958125172</v>
+        <v>21.94015976897271</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.6258881668004848</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.1951314199547214</v>
+        <v>-0.1951314200388242</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>324.3734949065143</v>
+        <v>324.3734949065144</v>
       </c>
       <c r="E134" s="2" t="n">
         <v>161</v>
@@ -7548,10 +7548,10 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>34.90317445982744</v>
+        <v>34.90317443963052</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>15.45578908541229</v>
+        <v>15.45578910327099</v>
       </c>
       <c r="J134" s="2" t="n">
         <v>0.6565710287312002</v>
@@ -7566,7 +7566,7 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-3.001775843989412</v>
+        <v>-3.001775843064267</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
@@ -7601,10 +7601,10 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>40.33738741777264</v>
+        <v>40.3373874265526</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>12.69121814700962</v>
+        <v>12.69121821500844</v>
       </c>
       <c r="J135" s="2" t="n">
         <v>0.6438098816768137</v>
@@ -7619,7 +7619,7 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-0.07208488523406575</v>
+        <v>-0.07208488525368989</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
@@ -7654,10 +7654,10 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>48.78337293561559</v>
+        <v>48.78337296322691</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>13.13478716827785</v>
+        <v>13.13478719312636</v>
       </c>
       <c r="J136" s="2" t="n">
         <v>0.4336194881723438</v>
@@ -7672,7 +7672,7 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.00135838433432525</v>
+        <v>0.001358384348340096</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
@@ -7707,10 +7707,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>46.98536351028262</v>
+        <v>46.98536343286383</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>9.361723858754344</v>
+        <v>9.361723948073466</v>
       </c>
       <c r="J137" s="2" t="n">
         <v>0.7008191880634951</v>
@@ -7725,7 +7725,7 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>0.05563271231144262</v>
+        <v>0.0556327124516125</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>315.8262163117213</v>
+        <v>315.8262163117209</v>
       </c>
       <c r="E138" s="2" t="n">
         <v>20.2</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>41.18178212825982</v>
+        <v>41.18178208585304</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>23.1699912176212</v>
+        <v>23.16999121126094</v>
       </c>
       <c r="J138" s="2" t="n">
         <v>1.666493268690568</v>
@@ -7778,7 +7778,7 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>0.005617954560779598</v>
+        <v>0.005617954518729262</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
@@ -7813,10 +7813,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>44.50644029818359</v>
+        <v>44.50644048825841</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>27.0368560118699</v>
+        <v>27.03685621378759</v>
       </c>
       <c r="J139" s="2" t="n">
         <v>1.393532787778166</v>
@@ -7831,7 +7831,7 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>-0.07150740708090406</v>
+        <v>-0.07150740715098969</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>311.8866643891916</v>
+        <v>311.8866643891915</v>
       </c>
       <c r="E140" s="2" t="n">
         <v>2375</v>
@@ -7866,10 +7866,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>39.31870039689782</v>
+        <v>39.31870040216755</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>16.45600864502109</v>
+        <v>16.45600866553784</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>1.112614675244695</v>
@@ -7884,7 +7884,7 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-51.13296654379819</v>
+        <v>-51.13296654099501</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>310.9196580101554</v>
+        <v>310.9196580101551</v>
       </c>
       <c r="E141" s="2" t="n">
         <v>13.05</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>29.79336397825612</v>
+        <v>29.79336409007895</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>26.50168138423483</v>
+        <v>26.50168131019128</v>
       </c>
       <c r="J141" s="2" t="n">
         <v>0.6891350105669644</v>
@@ -7937,7 +7937,7 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>-0.05104369893955318</v>
+        <v>-0.05104369888348503</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
@@ -7972,10 +7972,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>24.92037700340302</v>
+        <v>24.92037752250039</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>22.12926968164967</v>
+        <v>22.1292696529838</v>
       </c>
       <c r="J142" s="2" t="n">
         <v>0.5394939092582285</v>
@@ -7990,7 +7990,7 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-0.1883554859724312</v>
+        <v>-0.1883554858042342</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>42.65031856486448</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>13.04183025208686</v>
+        <v>13.04183028770342</v>
       </c>
       <c r="J143" s="2" t="n">
         <v>0.5556022504746785</v>
@@ -8064,7 +8064,7 @@
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>306.583345807528</v>
+        <v>306.5833458075277</v>
       </c>
       <c r="E144" s="2" t="n">
         <v>202.5</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>37.46864334229223</v>
+        <v>37.46864336814888</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>16.47024273729877</v>
+        <v>16.47024291365606</v>
       </c>
       <c r="J144" s="2" t="n">
         <v>0.7362759507559887</v>
@@ -8096,7 +8096,7 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>-2.499100636255259</v>
+        <v>-2.499100636423456</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
@@ -8131,10 +8131,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>54.1107262303526</v>
+        <v>54.11072630178572</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>30.01363641578784</v>
+        <v>30.01363640456347</v>
       </c>
       <c r="J145" s="2" t="n">
         <v>0.4636672827973987</v>
@@ -8149,7 +8149,7 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>0.07450240088033183</v>
+        <v>0.07450240086631213</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
@@ -8184,10 +8184,10 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>38.13450927348829</v>
+        <v>38.13450915356367</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>14.62620669631222</v>
+        <v>14.62620665395394</v>
       </c>
       <c r="J146" s="2" t="n">
         <v>0.1576787177624713</v>
@@ -8202,7 +8202,7 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>0.00672782186575055</v>
+        <v>0.0067278218937874</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v/>
       </c>
       <c r="D147" s="2" t="n">
-        <v>298.1043584702778</v>
+        <v>298.1043584702805</v>
       </c>
       <c r="E147" s="2" t="n">
         <v>21.7</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>28.47202098306909</v>
+        <v>28.47202074124175</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>38.17029030474674</v>
+        <v>38.17029022989863</v>
       </c>
       <c r="J147" s="2" t="n">
         <v>0.7064990804793668</v>
@@ -8255,7 +8255,7 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>-0.006367604103995173</v>
+        <v>-0.006367604146046313</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
@@ -8290,10 +8290,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>46.78619358041447</v>
+        <v>46.78619327419772</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>16.81437217199812</v>
+        <v>16.81437216953315</v>
       </c>
       <c r="J148" s="2" t="n">
         <v>0.7356774618727012</v>
@@ -8308,7 +8308,7 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-0.01929962177754729</v>
+        <v>-0.01929962095054544</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
@@ -8343,10 +8343,10 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>48.0457881643639</v>
+        <v>48.04578814501448</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>12.92841900142494</v>
+        <v>12.92841902566663</v>
       </c>
       <c r="J149" s="2" t="n">
         <v>0.6526902498242347</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>31.11965366107057</v>
+        <v>31.11965414377806</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>16.9798251926336</v>
+        <v>16.97982516631386</v>
       </c>
       <c r="J150" s="2" t="n">
         <v>1.236260956402194</v>
@@ -8449,10 +8449,10 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>44.77113506532987</v>
+        <v>44.77113489087118</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>14.83833217707708</v>
+        <v>14.83833210303942</v>
       </c>
       <c r="J151" s="2" t="n">
         <v>0.5362131154300699</v>
@@ -8467,7 +8467,7 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>0.007350385642111268</v>
+        <v>0.007350385639307809</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v/>
       </c>
       <c r="D152" s="2" t="n">
-        <v>290.117188654996</v>
+        <v>290.1171886549956</v>
       </c>
       <c r="E152" s="2" t="n">
         <v>54</v>
@@ -8502,10 +8502,10 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>47.671583319733</v>
+        <v>47.67158347510951</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>31.07176765520155</v>
+        <v>31.07176773131543</v>
       </c>
       <c r="J152" s="2" t="n">
         <v>0.3096566220677379</v>
@@ -8520,7 +8520,7 @@
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>-0.1998657333549062</v>
+        <v>-0.1998657338314843</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>39.3573987170837</v>
+        <v>39.35739908199829</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>12.3824139775034</v>
+        <v>12.38241420188877</v>
       </c>
       <c r="J153" s="2" t="n">
         <v>0.6994731586771628</v>
@@ -8573,7 +8573,7 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>-0.7093332781602362</v>
+        <v>-0.7093332784405721</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
@@ -8608,10 +8608,10 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>46.19626517597657</v>
+        <v>46.19626528475998</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>13.87327494046911</v>
+        <v>13.87327517568225</v>
       </c>
       <c r="J154" s="2" t="n">
         <v>1.138805565488487</v>
@@ -8626,7 +8626,7 @@
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>-2.066845917593995</v>
+        <v>-2.066845918715335</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>40.59893215530693</v>
+        <v>40.59893226524724</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>18.26385838011461</v>
+        <v>18.26385850035371</v>
       </c>
       <c r="J155" s="2" t="n">
         <v>0.7578812105384907</v>
@@ -8679,7 +8679,7 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>-0.3617820663626137</v>
+        <v>-0.361782066446718</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>35.8029008464582</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>16.78057255485419</v>
+        <v>16.78057251266094</v>
       </c>
       <c r="J156" s="2" t="n">
         <v>0.5639635384076626</v>
@@ -8732,7 +8732,7 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>-0.1071257818291205</v>
+        <v>-0.1071257818151046</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v/>
       </c>
       <c r="D157" s="2" t="n">
-        <v>280.9017236308256</v>
+        <v>280.9017236308257</v>
       </c>
       <c r="E157" s="2" t="n">
         <v>54.5</v>
@@ -8767,10 +8767,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>40.88434887201726</v>
+        <v>40.88434878834595</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>20.52121050859692</v>
+        <v>20.52121051728318</v>
       </c>
       <c r="J157" s="2" t="n">
         <v>0.4980778349485268</v>
@@ -8785,7 +8785,7 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>0.03109437756371164</v>
+        <v>0.03109437759174438</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>42.6463173221788</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>18.40229509550641</v>
+        <v>18.40229554433445</v>
       </c>
       <c r="J158" s="2" t="n">
         <v>0.5712335199885328</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>48.18687767363646</v>
+        <v>48.18687770745354</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>17.01715756025502</v>
+        <v>17.0171575197252</v>
       </c>
       <c r="J159" s="2" t="n">
         <v>0.7700800749447951</v>
@@ -8912,7 +8912,7 @@
         <v/>
       </c>
       <c r="D160" s="2" t="n">
-        <v>275.2654811912806</v>
+        <v>275.2654811912811</v>
       </c>
       <c r="E160" s="2" t="n">
         <v>39.75</v>
@@ -8926,10 +8926,10 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>42.12327264569419</v>
+        <v>42.12327347196172</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>17.42999733926875</v>
+        <v>17.42999735392688</v>
       </c>
       <c r="J160" s="2" t="n">
         <v>0.5067630713733464</v>
@@ -8944,7 +8944,7 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>-0.2251745776441927</v>
+        <v>-0.225174578288977</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v/>
       </c>
       <c r="D161" s="2" t="n">
-        <v>272.8714724102363</v>
+        <v>272.871472410239</v>
       </c>
       <c r="E161" s="2" t="n">
         <v>20.1</v>
@@ -8979,10 +8979,10 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>42.72964132358595</v>
+        <v>42.72964141574339</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>20.43073560220833</v>
+        <v>20.43073564676924</v>
       </c>
       <c r="J161" s="2" t="n">
         <v>0.8071419991133283</v>
@@ -8997,7 +8997,7 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>-0.02832837366376802</v>
+        <v>-0.02832837369180006</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>45.28411921492818</v>
+        <v>45.28411928864976</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>15.5221585796846</v>
+        <v>15.5221585047526</v>
       </c>
       <c r="J162" s="2" t="n">
         <v>0.3085982146732447</v>
@@ -9050,7 +9050,7 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>0.02260202212827608</v>
+        <v>0.02260202211425999</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v/>
       </c>
       <c r="D163" s="2" t="n">
-        <v>271.7964621146774</v>
+        <v>271.7964621146773</v>
       </c>
       <c r="E163" s="2" t="n">
         <v>12.05</v>
@@ -9088,7 +9088,7 @@
         <v>35.11584324334957</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>15.91601424236665</v>
+        <v>15.91601445783269</v>
       </c>
       <c r="J163" s="2" t="n">
         <v>0.5505321238124874</v>
@@ -9138,10 +9138,10 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>42.49082807179081</v>
+        <v>42.49082835831791</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>26.78804498581907</v>
+        <v>26.78804506192966</v>
       </c>
       <c r="J164" s="2" t="n">
         <v>0.863741978588675</v>
@@ -9156,7 +9156,7 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>-0.03573637602772788</v>
+        <v>-0.03573637604174305</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>45.6092396632764</v>
+        <v>45.6092396766642</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>8.083638410794652</v>
+        <v>8.083638377316912</v>
       </c>
       <c r="J165" s="2" t="n">
         <v>0.07304712403963563</v>
@@ -9209,7 +9209,7 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>-0.3545939540714455</v>
+        <v>-0.3545939545385542</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
@@ -9244,10 +9244,10 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>31.22291470919031</v>
+        <v>31.22291482907146</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>22.79551991477957</v>
+        <v>22.79552009103848</v>
       </c>
       <c r="J166" s="2" t="n">
         <v>1.256775495738611</v>
@@ -9262,7 +9262,7 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>-0.1886214288028349</v>
+        <v>-0.1886214290691568</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v/>
       </c>
       <c r="D167" s="2" t="n">
-        <v>259.9421763819296</v>
+        <v>259.9421763819298</v>
       </c>
       <c r="E167" s="2" t="n">
         <v>19.95</v>
@@ -9297,10 +9297,10 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>22.44512315373683</v>
+        <v>22.44512319492014</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>14.81479780793756</v>
+        <v>14.81479789325344</v>
       </c>
       <c r="J167" s="2" t="n">
         <v>2.202924728194796</v>
@@ -9315,7 +9315,7 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>-0.1078303464999892</v>
+        <v>-0.1078303465560581</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>36.69770628004311</v>
+        <v>36.69770633315134</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>19.12110368416399</v>
+        <v>19.12110379742091</v>
       </c>
       <c r="J168" s="2" t="n">
         <v>0.8464610782254472</v>
@@ -9368,7 +9368,7 @@
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>-0.05582737604972032</v>
+        <v>-0.05582737620390688</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v/>
       </c>
       <c r="D169" s="2" t="n">
-        <v>253.6303089698365</v>
+        <v>253.6303089698367</v>
       </c>
       <c r="E169" s="2" t="n">
         <v>26.75</v>
@@ -9403,10 +9403,10 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>42.51043329389953</v>
+        <v>42.51043337015093</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>17.34195182121777</v>
+        <v>17.34195192031239</v>
       </c>
       <c r="J169" s="2" t="n">
         <v>0.5219349141117053</v>
@@ -9421,7 +9421,7 @@
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>-0.1370553411435285</v>
+        <v>-0.1370553412276279</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v/>
       </c>
       <c r="D170" s="2" t="n">
-        <v>251.1022426870903</v>
+        <v>251.1022426870907</v>
       </c>
       <c r="E170" s="2" t="n">
         <v>23.15</v>
@@ -9456,10 +9456,10 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>44.46286740615979</v>
+        <v>44.46286744129706</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>20.89076563196143</v>
+        <v>20.8907657309504</v>
       </c>
       <c r="J170" s="2" t="n">
         <v>0.6154892070149406</v>
@@ -9474,7 +9474,7 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>-0.1573588321442507</v>
+        <v>-0.1573588322423693</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>37.04723301940401</v>
+        <v>37.04723298220243</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>13.25179518609877</v>
+        <v>13.25179515592214</v>
       </c>
       <c r="J171" s="2" t="n">
         <v>1.464353610775058</v>
@@ -9527,7 +9527,7 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>-0.1112275739025583</v>
+        <v>-0.1112275738064641</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
@@ -9562,10 +9562,10 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>38.51308094937624</v>
+        <v>38.51308082840315</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>18.40715959498293</v>
+        <v>18.40715962077695</v>
       </c>
       <c r="J172" s="2" t="n">
         <v>0.3244232281529167</v>
@@ -9580,7 +9580,7 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>-0.02202302400273082</v>
+        <v>-0.02202302396068179</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v/>
       </c>
       <c r="D173" s="2" t="n">
-        <v>242.1533977469897</v>
+        <v>242.1533977469896</v>
       </c>
       <c r="E173" s="2" t="n">
         <v>12.55</v>
@@ -9615,10 +9615,10 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>44.6892376664519</v>
+        <v>44.68923778387602</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>18.20686106443848</v>
+        <v>18.20686105869171</v>
       </c>
       <c r="J173" s="2" t="n">
         <v>0.3148614968311614</v>
@@ -9633,7 +9633,7 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>0.008548302122010659</v>
+        <v>0.00854830210799655</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>37.24393446335813</v>
+        <v>37.24393446726197</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>18.11233668192828</v>
+        <v>18.11233669785458</v>
       </c>
       <c r="J174" s="2" t="n">
         <v>0.6326361004628215</v>
@@ -9686,7 +9686,7 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-4.7098693513906</v>
+        <v>-4.709869351278456</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
@@ -9721,10 +9721,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>41.38079259369658</v>
+        <v>41.38079254902554</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>13.62126115478578</v>
+        <v>13.62126135493485</v>
       </c>
       <c r="J175" s="2" t="n">
         <v>1.42699443262022</v>
@@ -9760,7 +9760,7 @@
         <v/>
       </c>
       <c r="D176" s="2" t="n">
-        <v>240.1503147303318</v>
+        <v>240.1503147303322</v>
       </c>
       <c r="E176" s="2" t="n">
         <v>37.9</v>
@@ -9774,10 +9774,10 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>33.66191968225733</v>
+        <v>33.66191991735833</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>19.22685155149927</v>
+        <v>19.22685155625448</v>
       </c>
       <c r="J176" s="2" t="n">
         <v>1.181382082710356</v>
@@ -9792,7 +9792,7 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>-0.07602936351756642</v>
+        <v>-0.07602936358765058</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v/>
       </c>
       <c r="D177" s="2" t="n">
-        <v>239.8173842435572</v>
+        <v>239.8173842435586</v>
       </c>
       <c r="E177" s="2" t="n">
         <v>42.35</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>28.94825650379946</v>
+        <v>28.94825770079498</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>21.63508673341572</v>
+        <v>21.63508693520188</v>
       </c>
       <c r="J177" s="2" t="n">
         <v>0.6976685868789249</v>
@@ -9845,7 +9845,7 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>-0.1875961874180234</v>
+        <v>-0.187596187726399</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
@@ -9880,10 +9880,10 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>31.77941283232781</v>
+        <v>31.77941288068055</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>19.47919841181175</v>
+        <v>19.47919842426123</v>
       </c>
       <c r="J178" s="2" t="n">
         <v>0.587562598346256</v>
@@ -9898,7 +9898,7 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>-1.54719354991699</v>
+        <v>-1.547193550141268</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v/>
       </c>
       <c r="D179" s="2" t="n">
-        <v>228.2374235031965</v>
+        <v>228.2374235031967</v>
       </c>
       <c r="E179" s="2" t="n">
         <v>20</v>
@@ -9933,10 +9933,10 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>37.09061351554261</v>
+        <v>37.09061368411447</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>13.88209853251779</v>
+        <v>13.8820985469282</v>
       </c>
       <c r="J179" s="2" t="n">
         <v>3.939866485233143</v>
@@ -9951,7 +9951,7 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>-0.02465691947416643</v>
+        <v>-0.02465691944613531</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>41.70378718266276</v>
+        <v>41.70378719185739</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>13.23085047715677</v>
+        <v>13.23085062617259</v>
       </c>
       <c r="J180" s="2" t="n">
         <v>0.7129140251667055</v>
@@ -10004,7 +10004,7 @@
         <v>-1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>-1.412324573022615</v>
+        <v>-1.412324573050652</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
@@ -10039,10 +10039,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>26.40896598403125</v>
+        <v>26.40896600518654</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>17.36920756451368</v>
+        <v>17.36920757475094</v>
       </c>
       <c r="J181" s="2" t="n">
         <v>3.50443053353448</v>
@@ -10078,7 +10078,7 @@
         <v/>
       </c>
       <c r="D182" s="2" t="n">
-        <v>222.5842119254837</v>
+        <v>222.5842119254875</v>
       </c>
       <c r="E182" s="2" t="n">
         <v>452</v>
@@ -10092,10 +10092,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>30.04866702802165</v>
+        <v>30.0486670533417</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>16.46876598901444</v>
+        <v>16.46876615347733</v>
       </c>
       <c r="J182" s="2" t="n">
         <v>0.839323304081886</v>
@@ -10110,7 +10110,7 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>-10.01004099880906</v>
+        <v>-10.01004100035093</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v/>
       </c>
       <c r="D183" s="2" t="n">
-        <v>220.8383715041343</v>
+        <v>220.8383715041211</v>
       </c>
       <c r="E183" s="2" t="n">
         <v>22.3</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>32.25510680188508</v>
+        <v>32.25510723173078</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>18.52595021963575</v>
+        <v>18.52595030233048</v>
       </c>
       <c r="J183" s="2" t="n">
         <v>2.211570275507906</v>
@@ -10163,7 +10163,7 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>-0.08223432883422122</v>
+        <v>-0.08223432852584744</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
@@ -10198,10 +10198,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>17.75984924523473</v>
+        <v>17.75984912974734</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>31.07741294659516</v>
+        <v>31.07741285428129</v>
       </c>
       <c r="J184" s="2" t="n">
         <v>2.972903222633497</v>
@@ -10216,7 +10216,7 @@
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>-0.1302129739667506</v>
+        <v>-0.1302129738966683</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v/>
       </c>
       <c r="D185" s="2" t="n">
-        <v>219.6636854026522</v>
+        <v>219.6636854026523</v>
       </c>
       <c r="E185" s="2" t="n">
         <v>19.95</v>
@@ -10251,10 +10251,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>45.80047291734436</v>
+        <v>45.80047287899979</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>31.46990639360363</v>
+        <v>31.46990647098738</v>
       </c>
       <c r="J185" s="2" t="n">
         <v>1.108296147948073</v>
@@ -10269,7 +10269,7 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>-0.05245571655565151</v>
+        <v>-0.05245571652761932</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>42.08954314353697</v>
+        <v>42.08954310887667</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>18.16381154189959</v>
+        <v>18.16381154880786</v>
       </c>
       <c r="J186" s="2" t="n">
         <v>0.6861878957056818</v>
@@ -10322,7 +10322,7 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>-0.002582285144193119</v>
+        <v>-0.00258228511615971</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>39.07494390106422</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>32.03214066807779</v>
+        <v>32.03214070679566</v>
       </c>
       <c r="J187" s="2" t="n">
         <v>0.4909209318008714</v>
@@ -10428,7 +10428,7 @@
         <v>-1</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>0.1346724570547306</v>
+        <v>0.1346724574752436</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v/>
       </c>
       <c r="D189" s="2" t="n">
-        <v>212.3896173297932</v>
+        <v>212.3896173297947</v>
       </c>
       <c r="E189" s="2" t="n">
         <v>72.5</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>39.42819275435444</v>
+        <v>39.42819250772024</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>15.65605421188746</v>
+        <v>15.65605419117237</v>
       </c>
       <c r="J189" s="2" t="n">
         <v>0.4375476809749864</v>
@@ -10481,7 +10481,7 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>-0.4830976567189957</v>
+        <v>-0.4830976558779743</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
@@ -10516,10 +10516,10 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>42.44097579066319</v>
+        <v>42.44097588400535</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>17.66346573348508</v>
+        <v>17.66346532103762</v>
       </c>
       <c r="J190" s="2" t="n">
         <v>1.450463641969027</v>
@@ -10534,7 +10534,7 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>0.1774723637601874</v>
+        <v>0.1774723633396778</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v/>
       </c>
       <c r="D191" s="2" t="n">
-        <v>209.8315123190274</v>
+        <v>209.8315123190269</v>
       </c>
       <c r="E191" s="2" t="n">
         <v>14.15</v>
@@ -10569,10 +10569,10 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>31.76210750871984</v>
+        <v>31.76210757600036</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>34.67127585504368</v>
+        <v>34.67127587431732</v>
       </c>
       <c r="J191" s="2" t="n">
         <v>0.6739273895802724</v>
@@ -10587,7 +10587,7 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>-0.08624705956445156</v>
+        <v>-0.0862470595955922</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v/>
       </c>
       <c r="D192" s="2" t="n">
-        <v>208.5968595680792</v>
+        <v>208.5968595680796</v>
       </c>
       <c r="E192" s="2" t="n">
         <v>63.4</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>28.69402212679135</v>
+        <v>28.69402223616352</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>14.55528510701873</v>
+        <v>14.55528510797964</v>
       </c>
       <c r="J192" s="2" t="n">
         <v>4.350607407176821</v>
@@ -10640,7 +10640,7 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>-0.0726533075367734</v>
+        <v>-0.07265330764891376</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v/>
       </c>
       <c r="D193" s="2" t="n">
-        <v>203.8771633295405</v>
+        <v>203.877163329522</v>
       </c>
       <c r="E193" s="2" t="n">
         <v>32.4</v>
@@ -10675,10 +10675,10 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>26.20846421932288</v>
+        <v>26.20846429085972</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>28.77121565246326</v>
+        <v>28.77121575041243</v>
       </c>
       <c r="J193" s="2" t="n">
         <v>0.7723333354227283</v>
@@ -10693,7 +10693,7 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>-0.4847165094663946</v>
+        <v>-0.4847165095084438</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
@@ -10728,10 +10728,10 @@
         <v>0</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>38.1926660926482</v>
+        <v>38.19266603962116</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>21.83322299530197</v>
+        <v>21.83322288446023</v>
       </c>
       <c r="J194" s="2" t="n">
         <v>0.4454782689911795</v>
@@ -10746,7 +10746,7 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>0.04192334600733683</v>
+        <v>0.04192334604938808</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v/>
       </c>
       <c r="D195" s="2" t="n">
-        <v>200.9609826828923</v>
+        <v>200.9609826828924</v>
       </c>
       <c r="E195" s="2" t="n">
         <v>10.9</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>37.9555333298274</v>
+        <v>37.95553365955038</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>13.38740956706532</v>
+        <v>13.38740945890676</v>
       </c>
       <c r="J195" s="2" t="n">
         <v>0.5492390088508141</v>
@@ -10799,7 +10799,7 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>-0.001646766840627603</v>
+        <v>-0.001646766826609913</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v/>
       </c>
       <c r="D196" s="2" t="n">
-        <v>199.3919112956317</v>
+        <v>199.3919112956312</v>
       </c>
       <c r="E196" s="2" t="n">
         <v>5.72</v>
@@ -10834,7 +10834,7 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>46.75618630965812</v>
+        <v>46.75618627676688</v>
       </c>
       <c r="I196" s="2" t="n">
         <v>12.48077372219393</v>
@@ -10852,7 +10852,7 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>-0.004494334027160554</v>
+        <v>-0.004494334029963614</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
@@ -10887,10 +10887,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>46.40002847591983</v>
+        <v>46.40002853523057</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>17.25040218844584</v>
+        <v>17.25040221514363</v>
       </c>
       <c r="J197" s="2" t="n">
         <v>0.4759424045309933</v>
@@ -10905,7 +10905,7 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>-0.006527888606874602</v>
+        <v>-0.006527888620892043</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>41.87867340504025</v>
+        <v>41.87867325492979</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>15.95279241144987</v>
+        <v>15.95279243531539</v>
       </c>
       <c r="J198" s="2" t="n">
         <v>1.142096699665133</v>
@@ -10958,7 +10958,7 @@
         <v>-1</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>-0.097907056421321</v>
+        <v>-0.09790705628114832</v>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
@@ -10993,10 +10993,10 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>38.87834805795499</v>
+        <v>38.87834804889827</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>18.42256341733223</v>
+        <v>18.42256342468394</v>
       </c>
       <c r="J199" s="2" t="n">
         <v>0.3839234692110819</v>
@@ -11011,7 +11011,7 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>-0.002435727526597598</v>
+        <v>-0.00243572753104554</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v/>
       </c>
       <c r="D200" s="2" t="n">
-        <v>191.4944117793927</v>
+        <v>191.4944117793926</v>
       </c>
       <c r="E200" s="2" t="n">
         <v>33.25</v>
@@ -11046,10 +11046,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>41.0078774070325</v>
+        <v>41.00787753136347</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>16.20458577354</v>
+        <v>16.2045856412287</v>
       </c>
       <c r="J200" s="2" t="n">
         <v>1.383064542000918</v>
@@ -11085,7 +11085,7 @@
         <v/>
       </c>
       <c r="D201" s="2" t="n">
-        <v>186.3796320064386</v>
+        <v>186.3796320064385</v>
       </c>
       <c r="E201" s="2" t="n">
         <v>15.6</v>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>39.88403382936222</v>
+        <v>39.88403525219066</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>12.22125793998997</v>
+        <v>12.22125802449684</v>
       </c>
       <c r="J201" s="2" t="n">
         <v>0.792643094580515</v>
@@ -11117,7 +11117,7 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>-0.05493366182545115</v>
+        <v>-0.05493366202168886</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v/>
       </c>
       <c r="D202" s="2" t="n">
-        <v>186.3733606055331</v>
+        <v>186.3733606055345</v>
       </c>
       <c r="E202" s="2" t="n">
         <v>19.1</v>
@@ -11152,10 +11152,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>32.33710617992884</v>
+        <v>32.33710614839586</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>21.36854130071545</v>
+        <v>21.36854124095531</v>
       </c>
       <c r="J202" s="2" t="n">
         <v>0.8270837206060042</v>
@@ -11170,7 +11170,7 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>-0.1272076239989698</v>
+        <v>-0.1272076239849521</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v/>
       </c>
       <c r="D203" s="2" t="n">
-        <v>184.8365381036546</v>
+        <v>184.8365381036545</v>
       </c>
       <c r="E203" s="2" t="n">
         <v>0</v>
@@ -11205,10 +11205,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>27.17683073199214</v>
+        <v>27.17683070691544</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>6.638014683532312</v>
+        <v>6.63801438330983</v>
       </c>
       <c r="J203" s="2" t="n">
         <v>0.05274782807872908</v>
@@ -11223,7 +11223,7 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>-0.5869951429312369</v>
+        <v>-0.5869951428331182</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v/>
       </c>
       <c r="D204" s="2" t="n">
-        <v>171.4823683509875</v>
+        <v>171.4823683509887</v>
       </c>
       <c r="E204" s="2" t="n">
         <v>21</v>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>39.6243058188655</v>
+        <v>39.62430608027638</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>19.27084826549112</v>
+        <v>19.27084833335619</v>
       </c>
       <c r="J204" s="2" t="n">
         <v>1.072538322032064</v>
@@ -11276,7 +11276,7 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>-0.06243836396079144</v>
+        <v>-0.06243836425515273</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
@@ -11311,10 +11311,10 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>33.64017174771803</v>
+        <v>33.64017176808579</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>16.67189970675269</v>
+        <v>16.67189975134604</v>
       </c>
       <c r="J205" s="2" t="n">
         <v>0.5972830170111316</v>
@@ -11329,7 +11329,7 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>-0.2631703178204252</v>
+        <v>-0.2631703178484599</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
@@ -11364,10 +11364,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>35.23202537230371</v>
+        <v>35.23202487879659</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>12.79516018825631</v>
+        <v>12.79516021569962</v>
       </c>
       <c r="J206" s="2" t="n">
         <v>0.9070508501102035</v>
@@ -11382,7 +11382,7 @@
         <v>-1</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>-0.003783344539141392</v>
+        <v>-0.003783344511108781</v>
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
@@ -11417,10 +11417,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>42.81558605469316</v>
+        <v>42.81558601745849</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>16.56407140785111</v>
+        <v>16.56407156565909</v>
       </c>
       <c r="J207" s="2" t="n">
         <v>0.6375347548168641</v>
@@ -11435,7 +11435,7 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>-0.02750537204438702</v>
+        <v>-0.02750537197430195</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v/>
       </c>
       <c r="D208" s="2" t="n">
-        <v>154.5450137125839</v>
+        <v>154.5450137125842</v>
       </c>
       <c r="E208" s="2" t="n">
         <v>14.65</v>
@@ -11470,10 +11470,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>18.96720576132269</v>
+        <v>18.96720566449008</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>37.39077864790909</v>
+        <v>37.39077879600702</v>
       </c>
       <c r="J208" s="2" t="n">
         <v>1.092384673918033</v>
@@ -11488,7 +11488,7 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>-0.1601367443506303</v>
+        <v>-0.1601367443225956</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
@@ -11523,10 +11523,10 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>41.29094830590429</v>
+        <v>41.2909486344534</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>25.26412816901833</v>
+        <v>25.26412814046873</v>
       </c>
       <c r="J209" s="2" t="n">
         <v>0.8459612942539827</v>
@@ -11541,7 +11541,7 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>0.01984843322721414</v>
+        <v>0.01984843310106216</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v/>
       </c>
       <c r="D210" s="2" t="n">
-        <v>144.2879827442854</v>
+        <v>144.2879827442885</v>
       </c>
       <c r="E210" s="2" t="n">
         <v>37.4</v>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>26.32164098062599</v>
+        <v>26.32164103463542</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>32.66092500978933</v>
+        <v>32.6609249488914</v>
       </c>
       <c r="J210" s="2" t="n">
         <v>0.745224560901022</v>
@@ -11594,7 +11594,7 @@
         <v>-1</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>-0.5646813091339467</v>
+        <v>-0.5646813091900145</v>
       </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v/>
       </c>
       <c r="D211" s="2" t="n">
-        <v>135.6900848151696</v>
+        <v>135.6900848151694</v>
       </c>
       <c r="E211" s="2" t="n">
         <v>12</v>
@@ -11629,10 +11629,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>44.88476928444177</v>
+        <v>44.88476933518017</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>9.082671424787145</v>
+        <v>9.082671351511237</v>
       </c>
       <c r="J211" s="2" t="n">
         <v>0.8260426133082037</v>
@@ -11647,7 +11647,7 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>-0.006523559738418068</v>
+        <v>-0.006523559752435355</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -11682,10 +11682,10 @@
         <v>0</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>46.18787323076813</v>
+        <v>46.18787326122152</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>14.29837710249628</v>
+        <v>14.29837711036076</v>
       </c>
       <c r="J212" s="2" t="n">
         <v>0.864253147715654</v>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>33.28383884309672</v>
+        <v>33.28383878328412</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>19.43320486271731</v>
+        <v>19.43320477676862</v>
       </c>
       <c r="J213" s="2" t="n">
         <v>2.135439370534526</v>
@@ -11753,7 +11753,7 @@
         <v>-1</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>0.02310610613538633</v>
+        <v>0.02310610620547382</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
@@ -11788,10 +11788,10 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>35.15229542526544</v>
+        <v>35.15229538671683</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>15.41082166557939</v>
+        <v>15.4108215916075</v>
       </c>
       <c r="J214" s="2" t="n">
         <v>1.069602134262409</v>
@@ -11806,7 +11806,7 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>-0.3518631865391063</v>
+        <v>-0.3518631864830262</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v/>
       </c>
       <c r="D215" s="2" t="n">
-        <v>115.2125773873973</v>
+        <v>115.2125773873876</v>
       </c>
       <c r="E215" s="2" t="n">
         <v>13.1</v>
@@ -11841,10 +11841,10 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>31.46003673339682</v>
+        <v>31.46003657337813</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>17.36164502281333</v>
+        <v>17.36164497172853</v>
       </c>
       <c r="J215" s="2" t="n">
         <v>1.183900032201891</v>
@@ -11859,7 +11859,7 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>-0.05649243772052989</v>
+        <v>-0.05649243766446169</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v/>
       </c>
       <c r="D216" s="2" t="n">
-        <v>113.5413318792635</v>
+        <v>113.5413318792634</v>
       </c>
       <c r="E216" s="2" t="n">
         <v>42.2</v>
@@ -11894,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>35.9644703017505</v>
+        <v>35.96447041454245</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>13.93448790399938</v>
+        <v>13.93448796832948</v>
       </c>
       <c r="J216" s="2" t="n">
         <v>0.7470577939426497</v>
@@ -11912,7 +11912,7 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>-0.08797405754068605</v>
+        <v>-0.0879740576528239</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v/>
       </c>
       <c r="D217" s="2" t="n">
-        <v>111.4539935035338</v>
+        <v>111.4539935035296</v>
       </c>
       <c r="E217" s="2" t="n">
         <v>37.1</v>
@@ -11947,10 +11947,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>38.31474272550329</v>
+        <v>38.31474380574001</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>19.8072450481784</v>
+        <v>19.80724593356599</v>
       </c>
       <c r="J217" s="2" t="n">
         <v>1.140735053551617</v>
@@ -11965,7 +11965,7 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>-0.1600506821955281</v>
+        <v>-0.1600506851110634</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
@@ -12000,10 +12000,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>42.38747917495705</v>
+        <v>42.38747910795255</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>15.66224258807412</v>
+        <v>15.66224255298983</v>
       </c>
       <c r="J218" s="2" t="n">
         <v>0.6255690494344768</v>
@@ -12018,7 +12018,7 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>-0.4768592881885362</v>
+        <v>-0.4768592879922899</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v/>
       </c>
       <c r="D219" s="2" t="n">
-        <v>105.113375372524</v>
+        <v>105.113375372526</v>
       </c>
       <c r="E219" s="2" t="n">
         <v>16.05</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>29.15798030195127</v>
+        <v>29.15798016232297</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>17.40966640224034</v>
+        <v>17.40966634237176</v>
       </c>
       <c r="J219" s="2" t="n">
         <v>1.150704985032148</v>
@@ -12071,7 +12071,7 @@
         <v>-1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>-0.04504399110521273</v>
+        <v>-0.04504399106316009</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v/>
       </c>
       <c r="D220" s="2" t="n">
-        <v>66.75369853960517</v>
+        <v>66.75369853960726</v>
       </c>
       <c r="E220" s="2" t="n">
         <v>18.7</v>
@@ -12106,10 +12106,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>38.12981930813263</v>
+        <v>38.12981949518039</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>15.61728087996966</v>
+        <v>15.61728090954431</v>
       </c>
       <c r="J220" s="2" t="n">
         <v>1.175243358263186</v>
@@ -12124,7 +12124,7 @@
         <v>-1</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>-0.09810294767354874</v>
+        <v>-0.0981029477436364</v>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
@@ -12159,10 +12159,10 @@
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>49.03105048059314</v>
+        <v>49.03105046949712</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>23.20550705563988</v>
+        <v>23.20550701085406</v>
       </c>
       <c r="J221" s="2" t="n">
         <v>0.4789460092041708</v>
@@ -12198,7 +12198,7 @@
         <v/>
       </c>
       <c r="D222" s="2" t="n">
-        <v>44.97485238389897</v>
+        <v>44.97485238389896</v>
       </c>
       <c r="E222" s="2" t="n">
         <v>0</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>46.32490309461532</v>
+        <v>46.32490312620203</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>7.762997886991726</v>
+        <v>7.762998015613408</v>
       </c>
       <c r="J222" s="2" t="n">
         <v>0.02263961093409358</v>
@@ -12230,7 +12230,7 @@
         <v>-1</v>
       </c>
       <c r="N222" s="2" t="n">
-        <v>0.4088147424047737</v>
+        <v>0.4088147384239509</v>
       </c>
       <c r="O222" s="2" t="n">
         <v/>
@@ -12263,10 +12263,10 @@
         <v>0</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>36.03484575680191</v>
+        <v>36.03484589912411</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>19.10102546667142</v>
+        <v>19.10102546762247</v>
       </c>
       <c r="J223" s="2" t="n">
         <v>0.7159176433644101</v>
